--- a/output/version3/test/25-15/MARL/IL/RL-RL with pt (+comm+it)/(RL+RL) test results.xlsx
+++ b/output/version3/test/25-15/MARL/IL/RL-RL with pt (+comm+it)/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1047</v>
+        <v>1001</v>
       </c>
       <c r="C2" t="n">
-        <v>1234</v>
+        <v>1273</v>
       </c>
       <c r="D2" t="n">
-        <v>1010</v>
+        <v>1114</v>
       </c>
       <c r="E2" t="n">
-        <v>995</v>
+        <v>1017</v>
       </c>
       <c r="F2" t="n">
-        <v>1168</v>
+        <v>1199</v>
       </c>
       <c r="G2" t="n">
-        <v>1098</v>
+        <v>1133</v>
       </c>
       <c r="H2" t="n">
-        <v>1119</v>
+        <v>1124</v>
       </c>
       <c r="I2" t="n">
-        <v>1222</v>
+        <v>1094</v>
       </c>
       <c r="J2" t="n">
-        <v>1124</v>
+        <v>1049</v>
       </c>
       <c r="K2" t="n">
-        <v>1023</v>
+        <v>1094</v>
       </c>
       <c r="L2" t="n">
-        <v>1104</v>
+        <v>1109.8</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>1178</v>
+        <v>1100</v>
       </c>
       <c r="C3" t="n">
-        <v>1084</v>
+        <v>1117</v>
       </c>
       <c r="D3" t="n">
-        <v>1083</v>
+        <v>1058</v>
       </c>
       <c r="E3" t="n">
-        <v>892</v>
+        <v>1064</v>
       </c>
       <c r="F3" t="n">
-        <v>1148</v>
+        <v>1098</v>
       </c>
       <c r="G3" t="n">
-        <v>1114</v>
+        <v>1104</v>
       </c>
       <c r="H3" t="n">
-        <v>1243</v>
+        <v>1047</v>
       </c>
       <c r="I3" t="n">
-        <v>840</v>
+        <v>1025</v>
       </c>
       <c r="J3" t="n">
-        <v>1158</v>
+        <v>1064</v>
       </c>
       <c r="K3" t="n">
-        <v>888</v>
+        <v>1173</v>
       </c>
       <c r="L3" t="n">
-        <v>1062.8</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>1065</v>
+        <v>1029</v>
       </c>
       <c r="C4" t="n">
-        <v>962</v>
+        <v>1103</v>
       </c>
       <c r="D4" t="n">
-        <v>1047</v>
+        <v>897</v>
       </c>
       <c r="E4" t="n">
-        <v>1061</v>
+        <v>1113</v>
       </c>
       <c r="F4" t="n">
-        <v>1021</v>
+        <v>1034</v>
       </c>
       <c r="G4" t="n">
-        <v>985</v>
+        <v>1018</v>
       </c>
       <c r="H4" t="n">
+        <v>974</v>
+      </c>
+      <c r="I4" t="n">
         <v>1052</v>
       </c>
-      <c r="I4" t="n">
-        <v>965</v>
-      </c>
       <c r="J4" t="n">
-        <v>904</v>
+        <v>938</v>
       </c>
       <c r="K4" t="n">
-        <v>1049</v>
+        <v>1120</v>
       </c>
       <c r="L4" t="n">
-        <v>1011.1</v>
+        <v>1027.8</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>1066</v>
+        <v>887</v>
       </c>
       <c r="C5" t="n">
-        <v>911</v>
+        <v>1043</v>
       </c>
       <c r="D5" t="n">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="E5" t="n">
-        <v>845</v>
+        <v>825</v>
       </c>
       <c r="F5" t="n">
-        <v>919</v>
+        <v>1069</v>
       </c>
       <c r="G5" t="n">
-        <v>894</v>
+        <v>1018</v>
       </c>
       <c r="H5" t="n">
-        <v>868</v>
+        <v>900</v>
       </c>
       <c r="I5" t="n">
-        <v>876</v>
+        <v>904</v>
       </c>
       <c r="J5" t="n">
-        <v>854</v>
+        <v>966</v>
       </c>
       <c r="K5" t="n">
-        <v>1046</v>
+        <v>915</v>
       </c>
       <c r="L5" t="n">
-        <v>917.7</v>
+        <v>941.6</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>1085</v>
+        <v>1028</v>
       </c>
       <c r="C6" t="n">
-        <v>1053</v>
+        <v>1076</v>
       </c>
       <c r="D6" t="n">
-        <v>997</v>
+        <v>1233</v>
       </c>
       <c r="E6" t="n">
-        <v>1201</v>
+        <v>1153</v>
       </c>
       <c r="F6" t="n">
-        <v>1206</v>
+        <v>1045</v>
       </c>
       <c r="G6" t="n">
-        <v>1002</v>
+        <v>1067</v>
       </c>
       <c r="H6" t="n">
-        <v>994</v>
+        <v>980</v>
       </c>
       <c r="I6" t="n">
-        <v>1077</v>
+        <v>1046</v>
       </c>
       <c r="J6" t="n">
-        <v>974</v>
+        <v>1063</v>
       </c>
       <c r="K6" t="n">
-        <v>1121</v>
+        <v>1090</v>
       </c>
       <c r="L6" t="n">
-        <v>1071</v>
+        <v>1078.1</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>944</v>
+        <v>964</v>
       </c>
       <c r="C7" t="n">
-        <v>998</v>
+        <v>898</v>
       </c>
       <c r="D7" t="n">
-        <v>931</v>
+        <v>984</v>
       </c>
       <c r="E7" t="n">
-        <v>892</v>
+        <v>886</v>
       </c>
       <c r="F7" t="n">
-        <v>835</v>
+        <v>922</v>
       </c>
       <c r="G7" t="n">
-        <v>894</v>
+        <v>964</v>
       </c>
       <c r="H7" t="n">
-        <v>952</v>
+        <v>779</v>
       </c>
       <c r="I7" t="n">
-        <v>1002</v>
+        <v>972</v>
       </c>
       <c r="J7" t="n">
-        <v>900</v>
+        <v>959</v>
       </c>
       <c r="K7" t="n">
-        <v>931</v>
+        <v>940</v>
       </c>
       <c r="L7" t="n">
-        <v>927.9</v>
+        <v>926.8</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>995</v>
+        <v>1022</v>
       </c>
       <c r="C8" t="n">
-        <v>990</v>
+        <v>1036</v>
       </c>
       <c r="D8" t="n">
-        <v>1000</v>
+        <v>956</v>
       </c>
       <c r="E8" t="n">
-        <v>1078</v>
+        <v>1104</v>
       </c>
       <c r="F8" t="n">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="G8" t="n">
-        <v>931</v>
+        <v>1033</v>
       </c>
       <c r="H8" t="n">
-        <v>1089</v>
+        <v>987</v>
       </c>
       <c r="I8" t="n">
-        <v>959</v>
+        <v>966</v>
       </c>
       <c r="J8" t="n">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="K8" t="n">
-        <v>1050</v>
+        <v>1188</v>
       </c>
       <c r="L8" t="n">
-        <v>1014.5</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>936</v>
+        <v>946</v>
       </c>
       <c r="C9" t="n">
         <v>897</v>
       </c>
       <c r="D9" t="n">
+        <v>972</v>
+      </c>
+      <c r="E9" t="n">
         <v>844</v>
       </c>
-      <c r="E9" t="n">
-        <v>895</v>
-      </c>
       <c r="F9" t="n">
-        <v>1013</v>
+        <v>854</v>
       </c>
       <c r="G9" t="n">
-        <v>923</v>
+        <v>929</v>
       </c>
       <c r="H9" t="n">
-        <v>916</v>
+        <v>940</v>
       </c>
       <c r="I9" t="n">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="J9" t="n">
-        <v>1009</v>
+        <v>827</v>
       </c>
       <c r="K9" t="n">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="L9" t="n">
-        <v>935.3</v>
+        <v>913.4</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>1088</v>
+        <v>963</v>
       </c>
       <c r="C10" t="n">
-        <v>1009</v>
+        <v>1084</v>
       </c>
       <c r="D10" t="n">
-        <v>1011</v>
+        <v>1044</v>
       </c>
       <c r="E10" t="n">
-        <v>1060</v>
+        <v>1212</v>
       </c>
       <c r="F10" t="n">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="G10" t="n">
-        <v>1058</v>
+        <v>1067</v>
       </c>
       <c r="H10" t="n">
-        <v>989</v>
+        <v>942</v>
       </c>
       <c r="I10" t="n">
-        <v>1166</v>
+        <v>904</v>
       </c>
       <c r="J10" t="n">
-        <v>1095</v>
+        <v>969</v>
       </c>
       <c r="K10" t="n">
-        <v>1167</v>
+        <v>1017</v>
       </c>
       <c r="L10" t="n">
-        <v>1063.5</v>
+        <v>1019.3</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>1132</v>
+        <v>1063</v>
       </c>
       <c r="C11" t="n">
-        <v>1062</v>
+        <v>1005</v>
       </c>
       <c r="D11" t="n">
-        <v>1040</v>
+        <v>1124</v>
       </c>
       <c r="E11" t="n">
-        <v>1179</v>
+        <v>1012</v>
       </c>
       <c r="F11" t="n">
-        <v>1252</v>
+        <v>965</v>
       </c>
       <c r="G11" t="n">
-        <v>1154</v>
+        <v>1210</v>
       </c>
       <c r="H11" t="n">
-        <v>1042</v>
+        <v>1150</v>
       </c>
       <c r="I11" t="n">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="J11" t="n">
-        <v>1024</v>
+        <v>1060</v>
       </c>
       <c r="K11" t="n">
         <v>1047</v>
       </c>
       <c r="L11" t="n">
-        <v>1090.5</v>
+        <v>1061.2</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>1043</v>
+        <v>994</v>
       </c>
       <c r="C12" t="n">
-        <v>1251</v>
+        <v>1129</v>
       </c>
       <c r="D12" t="n">
-        <v>1262</v>
+        <v>1013</v>
       </c>
       <c r="E12" t="n">
-        <v>1206</v>
+        <v>1143</v>
       </c>
       <c r="F12" t="n">
-        <v>1140</v>
+        <v>1061</v>
       </c>
       <c r="G12" t="n">
-        <v>1124</v>
+        <v>978</v>
       </c>
       <c r="H12" t="n">
-        <v>988</v>
+        <v>1163</v>
       </c>
       <c r="I12" t="n">
-        <v>1171</v>
+        <v>1084</v>
       </c>
       <c r="J12" t="n">
-        <v>1133</v>
+        <v>1127</v>
       </c>
       <c r="K12" t="n">
-        <v>968</v>
+        <v>1208</v>
       </c>
       <c r="L12" t="n">
-        <v>1128.6</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>1046</v>
+        <v>1117</v>
       </c>
       <c r="C13" t="n">
-        <v>1096</v>
+        <v>1129</v>
       </c>
       <c r="D13" t="n">
-        <v>1132</v>
+        <v>1094</v>
       </c>
       <c r="E13" t="n">
-        <v>1152</v>
+        <v>1126</v>
       </c>
       <c r="F13" t="n">
-        <v>1183</v>
+        <v>1063</v>
       </c>
       <c r="G13" t="n">
-        <v>1089</v>
+        <v>1031</v>
       </c>
       <c r="H13" t="n">
-        <v>1046</v>
+        <v>1188</v>
       </c>
       <c r="I13" t="n">
-        <v>1265</v>
+        <v>1189</v>
       </c>
       <c r="J13" t="n">
+        <v>1212</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1181</v>
+      </c>
+      <c r="L13" t="n">
         <v>1133</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1039</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1118.1</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>942</v>
+        <v>858</v>
       </c>
       <c r="C14" t="n">
-        <v>1054</v>
+        <v>901</v>
       </c>
       <c r="D14" t="n">
-        <v>1001</v>
+        <v>1071</v>
       </c>
       <c r="E14" t="n">
-        <v>915</v>
+        <v>990</v>
       </c>
       <c r="F14" t="n">
-        <v>1234</v>
+        <v>951</v>
       </c>
       <c r="G14" t="n">
-        <v>951</v>
+        <v>992</v>
       </c>
       <c r="H14" t="n">
-        <v>962</v>
+        <v>967</v>
       </c>
       <c r="I14" t="n">
-        <v>1069</v>
+        <v>896</v>
       </c>
       <c r="J14" t="n">
-        <v>825</v>
+        <v>914</v>
       </c>
       <c r="K14" t="n">
-        <v>932</v>
+        <v>999</v>
       </c>
       <c r="L14" t="n">
-        <v>988.5</v>
+        <v>953.9</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>1030</v>
+        <v>1070</v>
       </c>
       <c r="C15" t="n">
-        <v>1043</v>
+        <v>1049</v>
       </c>
       <c r="D15" t="n">
-        <v>1155</v>
+        <v>1062</v>
       </c>
       <c r="E15" t="n">
-        <v>1008</v>
+        <v>1036</v>
       </c>
       <c r="F15" t="n">
-        <v>1033</v>
+        <v>1049</v>
       </c>
       <c r="G15" t="n">
-        <v>1027</v>
+        <v>968</v>
       </c>
       <c r="H15" t="n">
-        <v>933</v>
+        <v>997</v>
       </c>
       <c r="I15" t="n">
-        <v>1251</v>
+        <v>1031</v>
       </c>
       <c r="J15" t="n">
-        <v>992</v>
+        <v>1090</v>
       </c>
       <c r="K15" t="n">
-        <v>1045</v>
+        <v>1082</v>
       </c>
       <c r="L15" t="n">
-        <v>1051.7</v>
+        <v>1043.4</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>971</v>
+        <v>983</v>
       </c>
       <c r="C16" t="n">
-        <v>1029</v>
+        <v>1220</v>
       </c>
       <c r="D16" t="n">
-        <v>980</v>
+        <v>986</v>
       </c>
       <c r="E16" t="n">
-        <v>1063</v>
+        <v>1097</v>
       </c>
       <c r="F16" t="n">
-        <v>1032</v>
+        <v>1147</v>
       </c>
       <c r="G16" t="n">
-        <v>1228</v>
+        <v>1245</v>
       </c>
       <c r="H16" t="n">
-        <v>1031</v>
+        <v>1042</v>
       </c>
       <c r="I16" t="n">
-        <v>956</v>
+        <v>991</v>
       </c>
       <c r="J16" t="n">
-        <v>1183</v>
+        <v>1123</v>
       </c>
       <c r="K16" t="n">
-        <v>1053</v>
+        <v>988</v>
       </c>
       <c r="L16" t="n">
-        <v>1052.6</v>
+        <v>1082.2</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="C17" t="n">
-        <v>1003</v>
+        <v>1174</v>
       </c>
       <c r="D17" t="n">
-        <v>1014</v>
+        <v>886</v>
       </c>
       <c r="E17" t="n">
-        <v>1081</v>
+        <v>1159</v>
       </c>
       <c r="F17" t="n">
-        <v>947</v>
+        <v>1108</v>
       </c>
       <c r="G17" t="n">
-        <v>1212</v>
+        <v>1045</v>
       </c>
       <c r="H17" t="n">
-        <v>1050</v>
+        <v>1145</v>
       </c>
       <c r="I17" t="n">
-        <v>1160</v>
+        <v>1173</v>
       </c>
       <c r="J17" t="n">
-        <v>985</v>
+        <v>1034</v>
       </c>
       <c r="K17" t="n">
-        <v>1141</v>
+        <v>1001</v>
       </c>
       <c r="L17" t="n">
-        <v>1060.7</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
+        <v>1052</v>
+      </c>
+      <c r="C18" t="n">
+        <v>966</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1203</v>
+      </c>
+      <c r="E18" t="n">
+        <v>935</v>
+      </c>
+      <c r="F18" t="n">
         <v>996</v>
       </c>
-      <c r="C18" t="n">
-        <v>1001</v>
-      </c>
-      <c r="D18" t="n">
-        <v>993</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1001</v>
-      </c>
-      <c r="F18" t="n">
-        <v>949</v>
-      </c>
       <c r="G18" t="n">
-        <v>1164</v>
+        <v>1197</v>
       </c>
       <c r="H18" t="n">
-        <v>968</v>
+        <v>1117</v>
       </c>
       <c r="I18" t="n">
-        <v>790</v>
+        <v>950</v>
       </c>
       <c r="J18" t="n">
-        <v>1051</v>
+        <v>942</v>
       </c>
       <c r="K18" t="n">
-        <v>1024</v>
+        <v>1048</v>
       </c>
       <c r="L18" t="n">
-        <v>993.7</v>
+        <v>1040.6</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>1313</v>
+        <v>1111</v>
       </c>
       <c r="C19" t="n">
-        <v>1020</v>
+        <v>1037</v>
       </c>
       <c r="D19" t="n">
-        <v>992</v>
+        <v>1085</v>
       </c>
       <c r="E19" t="n">
-        <v>1060</v>
+        <v>1205</v>
       </c>
       <c r="F19" t="n">
+        <v>1033</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1171</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1281</v>
+      </c>
+      <c r="I19" t="n">
+        <v>993</v>
+      </c>
+      <c r="J19" t="n">
         <v>1102</v>
       </c>
-      <c r="G19" t="n">
-        <v>1102</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1028</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1017</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1008</v>
-      </c>
       <c r="K19" t="n">
-        <v>1130</v>
+        <v>1088</v>
       </c>
       <c r="L19" t="n">
-        <v>1077.2</v>
+        <v>1110.6</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>1151</v>
+        <v>1016</v>
       </c>
       <c r="C20" t="n">
-        <v>999</v>
+        <v>978</v>
       </c>
       <c r="D20" t="n">
-        <v>1164</v>
+        <v>1181</v>
       </c>
       <c r="E20" t="n">
-        <v>896</v>
+        <v>978</v>
       </c>
       <c r="F20" t="n">
-        <v>1214</v>
+        <v>1149</v>
       </c>
       <c r="G20" t="n">
-        <v>1066</v>
+        <v>919</v>
       </c>
       <c r="H20" t="n">
-        <v>881</v>
+        <v>1033</v>
       </c>
       <c r="I20" t="n">
-        <v>1168</v>
+        <v>1036</v>
       </c>
       <c r="J20" t="n">
-        <v>995</v>
+        <v>937</v>
       </c>
       <c r="K20" t="n">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="L20" t="n">
-        <v>1061.2</v>
+        <v>1030.8</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>1179</v>
+        <v>1085</v>
       </c>
       <c r="C21" t="n">
-        <v>1069</v>
+        <v>1134</v>
       </c>
       <c r="D21" t="n">
-        <v>1099</v>
+        <v>1123</v>
       </c>
       <c r="E21" t="n">
-        <v>1076</v>
+        <v>1107</v>
       </c>
       <c r="F21" t="n">
-        <v>1170</v>
+        <v>1156</v>
       </c>
       <c r="G21" t="n">
-        <v>1053</v>
+        <v>1133</v>
       </c>
       <c r="H21" t="n">
-        <v>1182</v>
+        <v>1061</v>
       </c>
       <c r="I21" t="n">
-        <v>1118</v>
+        <v>1083</v>
       </c>
       <c r="J21" t="n">
-        <v>1148</v>
+        <v>1054</v>
       </c>
       <c r="K21" t="n">
-        <v>1134</v>
+        <v>1031</v>
       </c>
       <c r="L21" t="n">
-        <v>1122.8</v>
+        <v>1096.7</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>1059</v>
+        <v>1076</v>
       </c>
       <c r="C22" t="n">
+        <v>1088</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1052</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1098</v>
+      </c>
+      <c r="F22" t="n">
+        <v>900</v>
+      </c>
+      <c r="G22" t="n">
         <v>984</v>
       </c>
-      <c r="D22" t="n">
-        <v>976</v>
-      </c>
-      <c r="E22" t="n">
-        <v>976</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1186</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1049</v>
-      </c>
       <c r="H22" t="n">
-        <v>970</v>
+        <v>1134</v>
       </c>
       <c r="I22" t="n">
-        <v>1075</v>
+        <v>1257</v>
       </c>
       <c r="J22" t="n">
-        <v>1267</v>
+        <v>1201</v>
       </c>
       <c r="K22" t="n">
-        <v>964</v>
+        <v>1014</v>
       </c>
       <c r="L22" t="n">
-        <v>1050.6</v>
+        <v>1080.4</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>1019</v>
+        <v>1004</v>
       </c>
       <c r="C23" t="n">
-        <v>976</v>
+        <v>923</v>
       </c>
       <c r="D23" t="n">
-        <v>938</v>
+        <v>1155</v>
       </c>
       <c r="E23" t="n">
-        <v>978</v>
+        <v>942</v>
       </c>
       <c r="F23" t="n">
-        <v>951</v>
+        <v>962</v>
       </c>
       <c r="G23" t="n">
-        <v>1001</v>
+        <v>1144</v>
       </c>
       <c r="H23" t="n">
-        <v>953</v>
+        <v>1041</v>
       </c>
       <c r="I23" t="n">
-        <v>950</v>
+        <v>984</v>
       </c>
       <c r="J23" t="n">
-        <v>1039</v>
+        <v>1063</v>
       </c>
       <c r="K23" t="n">
-        <v>994</v>
+        <v>949</v>
       </c>
       <c r="L23" t="n">
-        <v>979.9</v>
+        <v>1016.7</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>1060</v>
+        <v>1024</v>
       </c>
       <c r="C24" t="n">
-        <v>1117</v>
+        <v>889</v>
       </c>
       <c r="D24" t="n">
-        <v>1052</v>
+        <v>903</v>
       </c>
       <c r="E24" t="n">
-        <v>1191</v>
+        <v>1004</v>
       </c>
       <c r="F24" t="n">
-        <v>931</v>
+        <v>1105</v>
       </c>
       <c r="G24" t="n">
-        <v>1083</v>
+        <v>1002</v>
       </c>
       <c r="H24" t="n">
-        <v>1157</v>
+        <v>879</v>
       </c>
       <c r="I24" t="n">
-        <v>958</v>
+        <v>1110</v>
       </c>
       <c r="J24" t="n">
-        <v>1042</v>
+        <v>1148</v>
       </c>
       <c r="K24" t="n">
-        <v>998</v>
+        <v>973</v>
       </c>
       <c r="L24" t="n">
-        <v>1058.9</v>
+        <v>1003.7</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>1007</v>
+        <v>1029</v>
       </c>
       <c r="C25" t="n">
-        <v>1165</v>
+        <v>1063</v>
       </c>
       <c r="D25" t="n">
-        <v>1036</v>
+        <v>1104</v>
       </c>
       <c r="E25" t="n">
-        <v>1041</v>
+        <v>1171</v>
       </c>
       <c r="F25" t="n">
-        <v>1120</v>
+        <v>1009</v>
       </c>
       <c r="G25" t="n">
-        <v>1128</v>
+        <v>1075</v>
       </c>
       <c r="H25" t="n">
-        <v>1093</v>
+        <v>1169</v>
       </c>
       <c r="I25" t="n">
-        <v>1082</v>
+        <v>1147</v>
       </c>
       <c r="J25" t="n">
-        <v>1005</v>
+        <v>1156</v>
       </c>
       <c r="K25" t="n">
-        <v>1067</v>
+        <v>1035</v>
       </c>
       <c r="L25" t="n">
-        <v>1074.4</v>
+        <v>1095.8</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="C26" t="n">
-        <v>1012</v>
+        <v>959</v>
       </c>
       <c r="D26" t="n">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="E26" t="n">
-        <v>1113</v>
+        <v>963</v>
       </c>
       <c r="F26" t="n">
-        <v>1199</v>
+        <v>1098</v>
       </c>
       <c r="G26" t="n">
-        <v>903</v>
+        <v>998</v>
       </c>
       <c r="H26" t="n">
-        <v>1245</v>
+        <v>952</v>
       </c>
       <c r="I26" t="n">
-        <v>916</v>
+        <v>968</v>
       </c>
       <c r="J26" t="n">
-        <v>1050</v>
+        <v>1043</v>
       </c>
       <c r="K26" t="n">
-        <v>976</v>
+        <v>970</v>
       </c>
       <c r="L26" t="n">
-        <v>1033.4</v>
+        <v>986.5</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>1153</v>
+        <v>1182</v>
       </c>
       <c r="C27" t="n">
-        <v>1121</v>
+        <v>1051</v>
       </c>
       <c r="D27" t="n">
-        <v>1133</v>
+        <v>1086</v>
       </c>
       <c r="E27" t="n">
-        <v>1033</v>
+        <v>1222</v>
       </c>
       <c r="F27" t="n">
-        <v>1084</v>
+        <v>1100</v>
       </c>
       <c r="G27" t="n">
-        <v>1097</v>
+        <v>1077</v>
       </c>
       <c r="H27" t="n">
-        <v>1206</v>
+        <v>959</v>
       </c>
       <c r="I27" t="n">
-        <v>1221</v>
+        <v>1028</v>
       </c>
       <c r="J27" t="n">
-        <v>1177</v>
+        <v>1111</v>
       </c>
       <c r="K27" t="n">
-        <v>1208</v>
+        <v>1158</v>
       </c>
       <c r="L27" t="n">
-        <v>1143.3</v>
+        <v>1097.4</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>1037</v>
+        <v>947</v>
       </c>
       <c r="C28" t="n">
-        <v>1002</v>
+        <v>1049</v>
       </c>
       <c r="D28" t="n">
-        <v>1068</v>
+        <v>1027</v>
       </c>
       <c r="E28" t="n">
-        <v>1109</v>
+        <v>1102</v>
       </c>
       <c r="F28" t="n">
-        <v>1063</v>
+        <v>1021</v>
       </c>
       <c r="G28" t="n">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="H28" t="n">
-        <v>1010</v>
+        <v>1003</v>
       </c>
       <c r="I28" t="n">
-        <v>1025</v>
+        <v>978</v>
       </c>
       <c r="J28" t="n">
-        <v>1030</v>
+        <v>992</v>
       </c>
       <c r="K28" t="n">
-        <v>1110</v>
+        <v>984</v>
       </c>
       <c r="L28" t="n">
-        <v>1053.3</v>
+        <v>1017.9</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>873</v>
+        <v>1001</v>
       </c>
       <c r="C29" t="n">
-        <v>1000</v>
+        <v>1018</v>
       </c>
       <c r="D29" t="n">
-        <v>986</v>
+        <v>1139</v>
       </c>
       <c r="E29" t="n">
-        <v>974</v>
+        <v>996</v>
       </c>
       <c r="F29" t="n">
-        <v>969</v>
+        <v>1071</v>
       </c>
       <c r="G29" t="n">
-        <v>1127</v>
+        <v>1075</v>
       </c>
       <c r="H29" t="n">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="I29" t="n">
-        <v>1050</v>
+        <v>1125</v>
       </c>
       <c r="J29" t="n">
-        <v>1140</v>
+        <v>973</v>
       </c>
       <c r="K29" t="n">
-        <v>1005</v>
+        <v>1026</v>
       </c>
       <c r="L29" t="n">
-        <v>1009.8</v>
+        <v>1040.1</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>1139</v>
+        <v>1217</v>
       </c>
       <c r="C30" t="n">
-        <v>1029</v>
+        <v>993</v>
       </c>
       <c r="D30" t="n">
-        <v>1167</v>
+        <v>985</v>
       </c>
       <c r="E30" t="n">
-        <v>900</v>
+        <v>825</v>
       </c>
       <c r="F30" t="n">
-        <v>1150</v>
+        <v>1010</v>
       </c>
       <c r="G30" t="n">
-        <v>894</v>
+        <v>1102</v>
       </c>
       <c r="H30" t="n">
-        <v>877</v>
+        <v>980</v>
       </c>
       <c r="I30" t="n">
-        <v>992</v>
+        <v>1030</v>
       </c>
       <c r="J30" t="n">
-        <v>1104</v>
+        <v>908</v>
       </c>
       <c r="K30" t="n">
-        <v>958</v>
+        <v>1030</v>
       </c>
       <c r="L30" t="n">
-        <v>1021</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>1103</v>
+        <v>1278</v>
       </c>
       <c r="C31" t="n">
-        <v>1113</v>
+        <v>944</v>
       </c>
       <c r="D31" t="n">
-        <v>1047</v>
+        <v>963</v>
       </c>
       <c r="E31" t="n">
-        <v>1263</v>
+        <v>1211</v>
       </c>
       <c r="F31" t="n">
-        <v>1053</v>
+        <v>1086</v>
       </c>
       <c r="G31" t="n">
-        <v>1065</v>
+        <v>1166</v>
       </c>
       <c r="H31" t="n">
-        <v>1166</v>
+        <v>1125</v>
       </c>
       <c r="I31" t="n">
-        <v>1167</v>
+        <v>1072</v>
       </c>
       <c r="J31" t="n">
-        <v>950</v>
+        <v>1050</v>
       </c>
       <c r="K31" t="n">
-        <v>1024</v>
+        <v>944</v>
       </c>
       <c r="L31" t="n">
-        <v>1095.1</v>
+        <v>1083.9</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>1065</v>
+        <v>934</v>
       </c>
       <c r="C32" t="n">
-        <v>843</v>
+        <v>978</v>
       </c>
       <c r="D32" t="n">
-        <v>1013</v>
+        <v>947</v>
       </c>
       <c r="E32" t="n">
-        <v>899</v>
+        <v>989</v>
       </c>
       <c r="F32" t="n">
-        <v>843</v>
+        <v>960</v>
       </c>
       <c r="G32" t="n">
-        <v>1053</v>
+        <v>924</v>
       </c>
       <c r="H32" t="n">
-        <v>931</v>
+        <v>1047</v>
       </c>
       <c r="I32" t="n">
-        <v>976</v>
+        <v>967</v>
       </c>
       <c r="J32" t="n">
+        <v>1061</v>
+      </c>
+      <c r="K32" t="n">
         <v>896</v>
       </c>
-      <c r="K32" t="n">
-        <v>878</v>
-      </c>
       <c r="L32" t="n">
-        <v>939.7</v>
+        <v>970.3</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>1093</v>
+        <v>1189</v>
       </c>
       <c r="C33" t="n">
-        <v>1076</v>
+        <v>1087</v>
       </c>
       <c r="D33" t="n">
-        <v>1159</v>
+        <v>1000</v>
       </c>
       <c r="E33" t="n">
-        <v>880</v>
+        <v>1138</v>
       </c>
       <c r="F33" t="n">
-        <v>1116</v>
+        <v>991</v>
       </c>
       <c r="G33" t="n">
-        <v>932</v>
+        <v>985</v>
       </c>
       <c r="H33" t="n">
-        <v>1106</v>
+        <v>983</v>
       </c>
       <c r="I33" t="n">
-        <v>1062</v>
+        <v>976</v>
       </c>
       <c r="J33" t="n">
-        <v>956</v>
+        <v>950</v>
       </c>
       <c r="K33" t="n">
-        <v>1152</v>
+        <v>1035</v>
       </c>
       <c r="L33" t="n">
-        <v>1053.2</v>
+        <v>1033.4</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>1061</v>
+        <v>1024</v>
       </c>
       <c r="C34" t="n">
-        <v>1106</v>
+        <v>998</v>
       </c>
       <c r="D34" t="n">
-        <v>972</v>
+        <v>1113</v>
       </c>
       <c r="E34" t="n">
-        <v>1051</v>
+        <v>974</v>
       </c>
       <c r="F34" t="n">
-        <v>1212</v>
+        <v>1062</v>
       </c>
       <c r="G34" t="n">
-        <v>1066</v>
+        <v>1100</v>
       </c>
       <c r="H34" t="n">
-        <v>1098</v>
+        <v>954</v>
       </c>
       <c r="I34" t="n">
-        <v>1072</v>
+        <v>1014</v>
       </c>
       <c r="J34" t="n">
-        <v>1013</v>
+        <v>1108</v>
       </c>
       <c r="K34" t="n">
-        <v>1047</v>
+        <v>1060</v>
       </c>
       <c r="L34" t="n">
-        <v>1069.8</v>
+        <v>1040.7</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>1067</v>
+        <v>1007</v>
       </c>
       <c r="C35" t="n">
-        <v>1069</v>
+        <v>1104</v>
       </c>
       <c r="D35" t="n">
-        <v>1012</v>
+        <v>964</v>
       </c>
       <c r="E35" t="n">
-        <v>1075</v>
+        <v>1058</v>
       </c>
       <c r="F35" t="n">
-        <v>1045</v>
+        <v>1226</v>
       </c>
       <c r="G35" t="n">
-        <v>1079</v>
+        <v>984</v>
       </c>
       <c r="H35" t="n">
-        <v>1105</v>
+        <v>979</v>
       </c>
       <c r="I35" t="n">
-        <v>1003</v>
+        <v>1053</v>
       </c>
       <c r="J35" t="n">
-        <v>1064</v>
+        <v>993</v>
       </c>
       <c r="K35" t="n">
-        <v>1024</v>
+        <v>1043</v>
       </c>
       <c r="L35" t="n">
-        <v>1054.3</v>
+        <v>1041.1</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>956</v>
+        <v>1172</v>
       </c>
       <c r="C36" t="n">
-        <v>998</v>
+        <v>933</v>
       </c>
       <c r="D36" t="n">
-        <v>1031</v>
+        <v>963</v>
       </c>
       <c r="E36" t="n">
-        <v>1023</v>
+        <v>1039</v>
       </c>
       <c r="F36" t="n">
-        <v>1054</v>
+        <v>1126</v>
       </c>
       <c r="G36" t="n">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="H36" t="n">
-        <v>997</v>
+        <v>970</v>
       </c>
       <c r="I36" t="n">
-        <v>954</v>
+        <v>1050</v>
       </c>
       <c r="J36" t="n">
-        <v>1014</v>
+        <v>992</v>
       </c>
       <c r="K36" t="n">
-        <v>946</v>
+        <v>880</v>
       </c>
       <c r="L36" t="n">
-        <v>1002.7</v>
+        <v>1017.4</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>1012</v>
+        <v>944</v>
       </c>
       <c r="C37" t="n">
-        <v>1185</v>
+        <v>1020</v>
       </c>
       <c r="D37" t="n">
-        <v>991</v>
+        <v>976</v>
       </c>
       <c r="E37" t="n">
-        <v>1155</v>
+        <v>1050</v>
       </c>
       <c r="F37" t="n">
-        <v>1049</v>
+        <v>993</v>
       </c>
       <c r="G37" t="n">
-        <v>1087</v>
+        <v>1033</v>
       </c>
       <c r="H37" t="n">
-        <v>1307</v>
+        <v>948</v>
       </c>
       <c r="I37" t="n">
-        <v>1002</v>
+        <v>1157</v>
       </c>
       <c r="J37" t="n">
-        <v>874</v>
+        <v>1034</v>
       </c>
       <c r="K37" t="n">
-        <v>1040</v>
+        <v>1085</v>
       </c>
       <c r="L37" t="n">
-        <v>1070.2</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>1017</v>
+        <v>1040</v>
       </c>
       <c r="C38" t="n">
-        <v>939</v>
+        <v>1016</v>
       </c>
       <c r="D38" t="n">
-        <v>994</v>
+        <v>1121</v>
       </c>
       <c r="E38" t="n">
-        <v>1002</v>
+        <v>839</v>
       </c>
       <c r="F38" t="n">
-        <v>877</v>
+        <v>918</v>
       </c>
       <c r="G38" t="n">
-        <v>1062</v>
+        <v>941</v>
       </c>
       <c r="H38" t="n">
-        <v>964</v>
+        <v>1045</v>
       </c>
       <c r="I38" t="n">
-        <v>1001</v>
+        <v>949</v>
       </c>
       <c r="J38" t="n">
-        <v>966</v>
+        <v>1007</v>
       </c>
       <c r="K38" t="n">
-        <v>1000</v>
+        <v>1209</v>
       </c>
       <c r="L38" t="n">
-        <v>982.2</v>
+        <v>1008.5</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>947</v>
+        <v>856</v>
       </c>
       <c r="C39" t="n">
-        <v>1162</v>
+        <v>1277</v>
       </c>
       <c r="D39" t="n">
-        <v>988</v>
+        <v>994</v>
       </c>
       <c r="E39" t="n">
-        <v>969</v>
+        <v>884</v>
       </c>
       <c r="F39" t="n">
-        <v>1130</v>
+        <v>1007</v>
       </c>
       <c r="G39" t="n">
-        <v>993</v>
+        <v>1076</v>
       </c>
       <c r="H39" t="n">
-        <v>1006</v>
+        <v>954</v>
       </c>
       <c r="I39" t="n">
-        <v>1107</v>
+        <v>968</v>
       </c>
       <c r="J39" t="n">
-        <v>1089</v>
+        <v>1053</v>
       </c>
       <c r="K39" t="n">
-        <v>1104</v>
+        <v>1245</v>
       </c>
       <c r="L39" t="n">
-        <v>1049.5</v>
+        <v>1031.4</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>992</v>
+        <v>1105</v>
       </c>
       <c r="C40" t="n">
-        <v>1080</v>
+        <v>971</v>
       </c>
       <c r="D40" t="n">
-        <v>985</v>
+        <v>1087</v>
       </c>
       <c r="E40" t="n">
-        <v>1078</v>
+        <v>1059</v>
       </c>
       <c r="F40" t="n">
-        <v>1013</v>
+        <v>1084</v>
       </c>
       <c r="G40" t="n">
-        <v>1115</v>
+        <v>1134</v>
       </c>
       <c r="H40" t="n">
-        <v>973</v>
+        <v>1206</v>
       </c>
       <c r="I40" t="n">
-        <v>1309</v>
+        <v>1111</v>
       </c>
       <c r="J40" t="n">
-        <v>977</v>
+        <v>1018</v>
       </c>
       <c r="K40" t="n">
-        <v>1084</v>
+        <v>914</v>
       </c>
       <c r="L40" t="n">
-        <v>1060.6</v>
+        <v>1068.9</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>1003</v>
+        <v>1118</v>
       </c>
       <c r="C41" t="n">
-        <v>874</v>
+        <v>1033</v>
       </c>
       <c r="D41" t="n">
-        <v>1071</v>
+        <v>995</v>
       </c>
       <c r="E41" t="n">
-        <v>1057</v>
+        <v>1084</v>
       </c>
       <c r="F41" t="n">
-        <v>976</v>
+        <v>1068</v>
       </c>
       <c r="G41" t="n">
-        <v>880</v>
+        <v>1137</v>
       </c>
       <c r="H41" t="n">
-        <v>1228</v>
+        <v>950</v>
       </c>
       <c r="I41" t="n">
-        <v>900</v>
+        <v>1159</v>
       </c>
       <c r="J41" t="n">
-        <v>907</v>
+        <v>1076</v>
       </c>
       <c r="K41" t="n">
-        <v>963</v>
+        <v>1099</v>
       </c>
       <c r="L41" t="n">
-        <v>985.9</v>
+        <v>1071.9</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>981</v>
+        <v>936</v>
       </c>
       <c r="C42" t="n">
-        <v>964</v>
+        <v>1177</v>
       </c>
       <c r="D42" t="n">
-        <v>914</v>
+        <v>936</v>
       </c>
       <c r="E42" t="n">
-        <v>1052</v>
+        <v>1187</v>
       </c>
       <c r="F42" t="n">
-        <v>995</v>
+        <v>974</v>
       </c>
       <c r="G42" t="n">
-        <v>1173</v>
+        <v>1223</v>
       </c>
       <c r="H42" t="n">
-        <v>1063</v>
+        <v>1121</v>
       </c>
       <c r="I42" t="n">
-        <v>939</v>
+        <v>1046</v>
       </c>
       <c r="J42" t="n">
-        <v>1151</v>
+        <v>976</v>
       </c>
       <c r="K42" t="n">
-        <v>1021</v>
+        <v>1008</v>
       </c>
       <c r="L42" t="n">
-        <v>1025.3</v>
+        <v>1058.4</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>935</v>
+        <v>1137</v>
       </c>
       <c r="C43" t="n">
-        <v>1088</v>
+        <v>1036</v>
       </c>
       <c r="D43" t="n">
-        <v>1139</v>
+        <v>1002</v>
       </c>
       <c r="E43" t="n">
-        <v>1037</v>
+        <v>1102</v>
       </c>
       <c r="F43" t="n">
-        <v>1000</v>
+        <v>1056</v>
       </c>
       <c r="G43" t="n">
-        <v>1087</v>
+        <v>1169</v>
       </c>
       <c r="H43" t="n">
-        <v>1158</v>
+        <v>954</v>
       </c>
       <c r="I43" t="n">
-        <v>1031</v>
+        <v>1014</v>
       </c>
       <c r="J43" t="n">
-        <v>981</v>
+        <v>1034</v>
       </c>
       <c r="K43" t="n">
-        <v>1022</v>
+        <v>1120</v>
       </c>
       <c r="L43" t="n">
-        <v>1047.8</v>
+        <v>1062.4</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>1016</v>
+        <v>893</v>
       </c>
       <c r="C44" t="n">
-        <v>1111</v>
+        <v>1232</v>
       </c>
       <c r="D44" t="n">
-        <v>981</v>
+        <v>1072</v>
       </c>
       <c r="E44" t="n">
-        <v>1144</v>
+        <v>1294</v>
       </c>
       <c r="F44" t="n">
-        <v>991</v>
+        <v>953</v>
       </c>
       <c r="G44" t="n">
-        <v>1130</v>
+        <v>1037</v>
       </c>
       <c r="H44" t="n">
-        <v>1061</v>
+        <v>1221</v>
       </c>
       <c r="I44" t="n">
-        <v>1097</v>
+        <v>947</v>
       </c>
       <c r="J44" t="n">
-        <v>962</v>
+        <v>994</v>
       </c>
       <c r="K44" t="n">
-        <v>869</v>
+        <v>976</v>
       </c>
       <c r="L44" t="n">
-        <v>1036.2</v>
+        <v>1061.9</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>1235</v>
+        <v>1024</v>
       </c>
       <c r="C45" t="n">
-        <v>1196</v>
+        <v>948</v>
       </c>
       <c r="D45" t="n">
-        <v>1013</v>
+        <v>931</v>
       </c>
       <c r="E45" t="n">
-        <v>924</v>
+        <v>1108</v>
       </c>
       <c r="F45" t="n">
-        <v>1177</v>
+        <v>938</v>
       </c>
       <c r="G45" t="n">
-        <v>1024</v>
+        <v>1052</v>
       </c>
       <c r="H45" t="n">
-        <v>969</v>
+        <v>941</v>
       </c>
       <c r="I45" t="n">
-        <v>1005</v>
+        <v>1105</v>
       </c>
       <c r="J45" t="n">
-        <v>903</v>
+        <v>965</v>
       </c>
       <c r="K45" t="n">
-        <v>1063</v>
+        <v>904</v>
       </c>
       <c r="L45" t="n">
-        <v>1050.9</v>
+        <v>991.6</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>1258</v>
+        <v>1043</v>
       </c>
       <c r="C46" t="n">
-        <v>1064</v>
+        <v>1241</v>
       </c>
       <c r="D46" t="n">
-        <v>949</v>
+        <v>1123</v>
       </c>
       <c r="E46" t="n">
-        <v>1176</v>
+        <v>1051</v>
       </c>
       <c r="F46" t="n">
-        <v>1156</v>
+        <v>1032</v>
       </c>
       <c r="G46" t="n">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="H46" t="n">
-        <v>1069</v>
+        <v>1059</v>
       </c>
       <c r="I46" t="n">
-        <v>1244</v>
+        <v>1141</v>
       </c>
       <c r="J46" t="n">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="K46" t="n">
-        <v>1137</v>
+        <v>1094</v>
       </c>
       <c r="L46" t="n">
-        <v>1131.5</v>
+        <v>1105.1</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>1059</v>
+        <v>1131</v>
       </c>
       <c r="C47" t="n">
+        <v>977</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1153</v>
+      </c>
+      <c r="E47" t="n">
+        <v>960</v>
+      </c>
+      <c r="F47" t="n">
+        <v>995</v>
+      </c>
+      <c r="G47" t="n">
+        <v>972</v>
+      </c>
+      <c r="H47" t="n">
+        <v>950</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1073</v>
+      </c>
+      <c r="J47" t="n">
         <v>1100</v>
       </c>
-      <c r="D47" t="n">
-        <v>1040</v>
-      </c>
-      <c r="E47" t="n">
-        <v>1181</v>
-      </c>
-      <c r="F47" t="n">
-        <v>1133</v>
-      </c>
-      <c r="G47" t="n">
-        <v>1055</v>
-      </c>
-      <c r="H47" t="n">
-        <v>958</v>
-      </c>
-      <c r="I47" t="n">
-        <v>917</v>
-      </c>
-      <c r="J47" t="n">
-        <v>1097</v>
-      </c>
       <c r="K47" t="n">
-        <v>1074</v>
+        <v>1023</v>
       </c>
       <c r="L47" t="n">
-        <v>1061.4</v>
+        <v>1033.4</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>1054</v>
+        <v>1104</v>
       </c>
       <c r="C48" t="n">
-        <v>1121</v>
+        <v>1000</v>
       </c>
       <c r="D48" t="n">
-        <v>1141</v>
+        <v>1057</v>
       </c>
       <c r="E48" t="n">
-        <v>1100</v>
+        <v>1135</v>
       </c>
       <c r="F48" t="n">
-        <v>1066</v>
+        <v>1078</v>
       </c>
       <c r="G48" t="n">
-        <v>1007</v>
+        <v>1130</v>
       </c>
       <c r="H48" t="n">
-        <v>1138</v>
+        <v>1000</v>
       </c>
       <c r="I48" t="n">
-        <v>1035</v>
+        <v>1027</v>
       </c>
       <c r="J48" t="n">
-        <v>1227</v>
+        <v>1061</v>
       </c>
       <c r="K48" t="n">
-        <v>1091</v>
+        <v>1161</v>
       </c>
       <c r="L48" t="n">
-        <v>1098</v>
+        <v>1075.3</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>1030</v>
+        <v>947</v>
       </c>
       <c r="C49" t="n">
-        <v>1064</v>
+        <v>1068</v>
       </c>
       <c r="D49" t="n">
-        <v>988</v>
+        <v>934</v>
       </c>
       <c r="E49" t="n">
-        <v>1112</v>
+        <v>949</v>
       </c>
       <c r="F49" t="n">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="G49" t="n">
-        <v>1073</v>
+        <v>1118</v>
       </c>
       <c r="H49" t="n">
-        <v>1123</v>
+        <v>1268</v>
       </c>
       <c r="I49" t="n">
-        <v>1136</v>
+        <v>1026</v>
       </c>
       <c r="J49" t="n">
-        <v>1037</v>
+        <v>1031</v>
       </c>
       <c r="K49" t="n">
-        <v>1059</v>
+        <v>1108</v>
       </c>
       <c r="L49" t="n">
-        <v>1067.8</v>
+        <v>1050.4</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>1046</v>
+        <v>894</v>
       </c>
       <c r="C50" t="n">
-        <v>1167</v>
+        <v>927</v>
       </c>
       <c r="D50" t="n">
-        <v>876</v>
+        <v>916</v>
       </c>
       <c r="E50" t="n">
-        <v>1086</v>
+        <v>967</v>
       </c>
       <c r="F50" t="n">
-        <v>1103</v>
+        <v>1053</v>
       </c>
       <c r="G50" t="n">
-        <v>909</v>
+        <v>930</v>
       </c>
       <c r="H50" t="n">
-        <v>891</v>
+        <v>1029</v>
       </c>
       <c r="I50" t="n">
-        <v>936</v>
+        <v>1238</v>
       </c>
       <c r="J50" t="n">
-        <v>1011</v>
+        <v>863</v>
       </c>
       <c r="K50" t="n">
-        <v>903</v>
+        <v>1003</v>
       </c>
       <c r="L50" t="n">
-        <v>992.8</v>
+        <v>982</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>1082</v>
+        <v>1103</v>
       </c>
       <c r="C51" t="n">
-        <v>974</v>
+        <v>949</v>
       </c>
       <c r="D51" t="n">
-        <v>1104</v>
+        <v>1022</v>
       </c>
       <c r="E51" t="n">
-        <v>1046</v>
+        <v>979</v>
       </c>
       <c r="F51" t="n">
-        <v>1056</v>
+        <v>1016</v>
       </c>
       <c r="G51" t="n">
-        <v>948</v>
+        <v>1015</v>
       </c>
       <c r="H51" t="n">
-        <v>1144</v>
+        <v>1000</v>
       </c>
       <c r="I51" t="n">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="J51" t="n">
-        <v>968</v>
+        <v>977</v>
       </c>
       <c r="K51" t="n">
-        <v>934</v>
+        <v>975</v>
       </c>
       <c r="L51" t="n">
-        <v>1021.2</v>
+        <v>999.5</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1050.38</v>
+        <v>1032.06</v>
       </c>
       <c r="C52" t="n">
-        <v>1049.3</v>
+        <v>1043.96</v>
       </c>
       <c r="D52" t="n">
-        <v>1027.96</v>
+        <v>1033.38</v>
       </c>
       <c r="E52" t="n">
-        <v>1043.62</v>
+        <v>1047.72</v>
       </c>
       <c r="F52" t="n">
-        <v>1067.14</v>
+        <v>1037.58</v>
       </c>
       <c r="G52" t="n">
-        <v>1045.86</v>
+        <v>1060.1</v>
       </c>
       <c r="H52" t="n">
-        <v>1045.46</v>
+        <v>1032.3</v>
       </c>
       <c r="I52" t="n">
-        <v>1042.82</v>
+        <v>1040.48</v>
       </c>
       <c r="J52" t="n">
-        <v>1031.82</v>
+        <v>1031.32</v>
       </c>
       <c r="K52" t="n">
-        <v>1030.46</v>
+        <v>1043.14</v>
       </c>
       <c r="L52" t="n">
-        <v>1043.482</v>
+        <v>1040.204</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>11.80238556861877</v>
+        <v>13.10528349876404</v>
       </c>
       <c r="C2" t="n">
-        <v>16.46593379974365</v>
+        <v>17.49456095695496</v>
       </c>
       <c r="D2" t="n">
-        <v>12.5838770866394</v>
+        <v>12.01401424407959</v>
       </c>
       <c r="E2" t="n">
-        <v>11.8999559879303</v>
+        <v>12.08476376533508</v>
       </c>
       <c r="F2" t="n">
-        <v>14.09256672859192</v>
+        <v>12.52863836288452</v>
       </c>
       <c r="G2" t="n">
-        <v>12.90999913215637</v>
+        <v>12.56056308746338</v>
       </c>
       <c r="H2" t="n">
-        <v>11.95400166511536</v>
+        <v>12.67079257965088</v>
       </c>
       <c r="I2" t="n">
-        <v>13.16528987884521</v>
+        <v>13.02586197853088</v>
       </c>
       <c r="J2" t="n">
-        <v>12.25774025917053</v>
+        <v>11.46126389503479</v>
       </c>
       <c r="K2" t="n">
-        <v>12.16107058525085</v>
+        <v>11.51469469070435</v>
       </c>
       <c r="L2" t="n">
-        <v>12.92928206920624</v>
+        <v>12.84604370594025</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>12.08342742919922</v>
+        <v>11.50924897193909</v>
       </c>
       <c r="C3" t="n">
-        <v>12.79617714881897</v>
+        <v>12.06495404243469</v>
       </c>
       <c r="D3" t="n">
-        <v>10.89388799667358</v>
+        <v>10.25290846824646</v>
       </c>
       <c r="E3" t="n">
-        <v>12.07739186286926</v>
+        <v>11.69604325294495</v>
       </c>
       <c r="F3" t="n">
-        <v>10.61134815216064</v>
+        <v>11.46981692314148</v>
       </c>
       <c r="G3" t="n">
-        <v>11.1901319026947</v>
+        <v>11.15759778022766</v>
       </c>
       <c r="H3" t="n">
-        <v>16.51100921630859</v>
+        <v>11.62840008735657</v>
       </c>
       <c r="I3" t="n">
-        <v>10.42912149429321</v>
+        <v>10.35416841506958</v>
       </c>
       <c r="J3" t="n">
-        <v>14.00884246826172</v>
+        <v>11.873783826828</v>
       </c>
       <c r="K3" t="n">
-        <v>11.03736019134521</v>
+        <v>14.06308317184448</v>
       </c>
       <c r="L3" t="n">
-        <v>12.16386978626251</v>
+        <v>11.6070004940033</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>13.6305775642395</v>
+        <v>13.68697667121887</v>
       </c>
       <c r="C4" t="n">
-        <v>12.63943552970886</v>
+        <v>12.90154528617859</v>
       </c>
       <c r="D4" t="n">
-        <v>14.56911706924438</v>
+        <v>11.72273755073547</v>
       </c>
       <c r="E4" t="n">
-        <v>12.58340334892273</v>
+        <v>13.35950875282288</v>
       </c>
       <c r="F4" t="n">
-        <v>13.93740224838257</v>
+        <v>11.82991361618042</v>
       </c>
       <c r="G4" t="n">
-        <v>12.29144048690796</v>
+        <v>13.14057326316833</v>
       </c>
       <c r="H4" t="n">
-        <v>12.80113124847412</v>
+        <v>12.48023223876953</v>
       </c>
       <c r="I4" t="n">
-        <v>11.08966875076294</v>
+        <v>11.62207365036011</v>
       </c>
       <c r="J4" t="n">
-        <v>12.57563495635986</v>
+        <v>12.32051038742065</v>
       </c>
       <c r="K4" t="n">
-        <v>12.43415307998657</v>
+        <v>13.21164536476135</v>
       </c>
       <c r="L4" t="n">
-        <v>12.85519642829895</v>
+        <v>12.62757167816162</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>14.45451927185059</v>
+        <v>10.64438700675964</v>
       </c>
       <c r="C5" t="n">
-        <v>10.36701607704163</v>
+        <v>15.57350301742554</v>
       </c>
       <c r="D5" t="n">
-        <v>11.12995862960815</v>
+        <v>10.28124165534973</v>
       </c>
       <c r="E5" t="n">
-        <v>11.33095669746399</v>
+        <v>10.07890129089355</v>
       </c>
       <c r="F5" t="n">
-        <v>11.01863074302673</v>
+        <v>11.68929266929626</v>
       </c>
       <c r="G5" t="n">
-        <v>10.64470672607422</v>
+        <v>12.03240752220154</v>
       </c>
       <c r="H5" t="n">
-        <v>10.50527310371399</v>
+        <v>10.96313381195068</v>
       </c>
       <c r="I5" t="n">
-        <v>10.1343822479248</v>
+        <v>10.38304853439331</v>
       </c>
       <c r="J5" t="n">
-        <v>11.86315083503723</v>
+        <v>10.87785148620605</v>
       </c>
       <c r="K5" t="n">
-        <v>11.37894868850708</v>
+        <v>10.84693646430969</v>
       </c>
       <c r="L5" t="n">
-        <v>11.28275430202484</v>
+        <v>11.3370703458786</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>12.50703835487366</v>
+        <v>11.42594695091248</v>
       </c>
       <c r="C6" t="n">
-        <v>12.40346527099609</v>
+        <v>12.06483387947083</v>
       </c>
       <c r="D6" t="n">
-        <v>11.15193581581116</v>
+        <v>11.99397683143616</v>
       </c>
       <c r="E6" t="n">
-        <v>14.28632879257202</v>
+        <v>14.59389400482178</v>
       </c>
       <c r="F6" t="n">
-        <v>14.81685066223145</v>
+        <v>12.16554737091064</v>
       </c>
       <c r="G6" t="n">
-        <v>11.48435735702515</v>
+        <v>11.80999159812927</v>
       </c>
       <c r="H6" t="n">
-        <v>11.53964948654175</v>
+        <v>11.95509719848633</v>
       </c>
       <c r="I6" t="n">
-        <v>12.77348637580872</v>
+        <v>12.56110215187073</v>
       </c>
       <c r="J6" t="n">
-        <v>11.53690242767334</v>
+        <v>12.66477108001709</v>
       </c>
       <c r="K6" t="n">
-        <v>12.96141171455383</v>
+        <v>12.95849895477295</v>
       </c>
       <c r="L6" t="n">
-        <v>12.54614262580872</v>
+        <v>12.41936600208282</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>11.15705156326294</v>
+        <v>11.9992847442627</v>
       </c>
       <c r="C7" t="n">
-        <v>11.71746158599854</v>
+        <v>11.55460786819458</v>
       </c>
       <c r="D7" t="n">
-        <v>11.39308881759644</v>
+        <v>11.80546021461487</v>
       </c>
       <c r="E7" t="n">
-        <v>11.6355128288269</v>
+        <v>11.63744354248047</v>
       </c>
       <c r="F7" t="n">
-        <v>10.90596413612366</v>
+        <v>11.0792920589447</v>
       </c>
       <c r="G7" t="n">
-        <v>11.29506969451904</v>
+        <v>12.41148519515991</v>
       </c>
       <c r="H7" t="n">
-        <v>11.36545729637146</v>
+        <v>11.24242210388184</v>
       </c>
       <c r="I7" t="n">
-        <v>10.74199628829956</v>
+        <v>11.05486273765564</v>
       </c>
       <c r="J7" t="n">
-        <v>11.867995262146</v>
+        <v>11.31669616699219</v>
       </c>
       <c r="K7" t="n">
-        <v>10.68002271652222</v>
+        <v>11.38104891777039</v>
       </c>
       <c r="L7" t="n">
-        <v>11.27596201896668</v>
+        <v>11.54826035499573</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>11.88033199310303</v>
+        <v>12.05636858940125</v>
       </c>
       <c r="C8" t="n">
-        <v>12.7380690574646</v>
+        <v>11.99048495292664</v>
       </c>
       <c r="D8" t="n">
-        <v>10.86314034461975</v>
+        <v>11.37593293190002</v>
       </c>
       <c r="E8" t="n">
-        <v>11.10374236106873</v>
+        <v>11.9045934677124</v>
       </c>
       <c r="F8" t="n">
-        <v>11.36271739006042</v>
+        <v>12.77279615402222</v>
       </c>
       <c r="G8" t="n">
-        <v>11.91548371315002</v>
+        <v>11.36594557762146</v>
       </c>
       <c r="H8" t="n">
-        <v>12.24557995796204</v>
+        <v>11.88466310501099</v>
       </c>
       <c r="I8" t="n">
-        <v>11.15898203849792</v>
+        <v>11.40188598632812</v>
       </c>
       <c r="J8" t="n">
-        <v>11.54526543617249</v>
+        <v>11.08620858192444</v>
       </c>
       <c r="K8" t="n">
-        <v>11.16307687759399</v>
+        <v>14.30731129646301</v>
       </c>
       <c r="L8" t="n">
-        <v>11.5976389169693</v>
+        <v>12.01461906433105</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>11.51756167411804</v>
+        <v>11.42928099632263</v>
       </c>
       <c r="C9" t="n">
-        <v>10.29330110549927</v>
+        <v>10.31671643257141</v>
       </c>
       <c r="D9" t="n">
-        <v>10.14617586135864</v>
+        <v>12.35043978691101</v>
       </c>
       <c r="E9" t="n">
-        <v>11.29782843589783</v>
+        <v>11.24483323097229</v>
       </c>
       <c r="F9" t="n">
-        <v>12.06618118286133</v>
+        <v>10.96230125427246</v>
       </c>
       <c r="G9" t="n">
-        <v>12.07027316093445</v>
+        <v>14.08541178703308</v>
       </c>
       <c r="H9" t="n">
-        <v>12.8097026348114</v>
+        <v>10.99749135971069</v>
       </c>
       <c r="I9" t="n">
-        <v>11.87896180152893</v>
+        <v>10.67726254463196</v>
       </c>
       <c r="J9" t="n">
-        <v>10.35117983818054</v>
+        <v>10.97450184822083</v>
       </c>
       <c r="K9" t="n">
-        <v>11.32585144042969</v>
+        <v>12.51411294937134</v>
       </c>
       <c r="L9" t="n">
-        <v>11.37570171356201</v>
+        <v>11.55523521900177</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>13.9557249546051</v>
+        <v>11.91257476806641</v>
       </c>
       <c r="C10" t="n">
-        <v>12.66534638404846</v>
+        <v>12.70062255859375</v>
       </c>
       <c r="D10" t="n">
-        <v>12.8888680934906</v>
+        <v>12.26213788986206</v>
       </c>
       <c r="E10" t="n">
-        <v>12.6826114654541</v>
+        <v>16.28721714019775</v>
       </c>
       <c r="F10" t="n">
-        <v>13.64433693885803</v>
+        <v>12.86762189865112</v>
       </c>
       <c r="G10" t="n">
-        <v>12.05616617202759</v>
+        <v>12.30558848381042</v>
       </c>
       <c r="H10" t="n">
-        <v>12.36682415008545</v>
+        <v>11.50961399078369</v>
       </c>
       <c r="I10" t="n">
-        <v>12.15229463577271</v>
+        <v>10.92113471031189</v>
       </c>
       <c r="J10" t="n">
-        <v>11.99486064910889</v>
+        <v>11.98698568344116</v>
       </c>
       <c r="K10" t="n">
-        <v>12.88259315490723</v>
+        <v>11.39301705360413</v>
       </c>
       <c r="L10" t="n">
-        <v>12.72896265983582</v>
+        <v>12.41465141773224</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>12.22302007675171</v>
+        <v>14.44630360603333</v>
       </c>
       <c r="C11" t="n">
-        <v>11.92458248138428</v>
+        <v>12.09527540206909</v>
       </c>
       <c r="D11" t="n">
-        <v>12.15257859230042</v>
+        <v>11.64936828613281</v>
       </c>
       <c r="E11" t="n">
-        <v>17.437420129776</v>
+        <v>11.71774792671204</v>
       </c>
       <c r="F11" t="n">
-        <v>18.94678854942322</v>
+        <v>12.12808775901794</v>
       </c>
       <c r="G11" t="n">
-        <v>16.48457384109497</v>
+        <v>12.45525360107422</v>
       </c>
       <c r="H11" t="n">
-        <v>12.04414510726929</v>
+        <v>13.05831027030945</v>
       </c>
       <c r="I11" t="n">
-        <v>11.94186353683472</v>
+        <v>11.68128538131714</v>
       </c>
       <c r="J11" t="n">
-        <v>12.1506404876709</v>
+        <v>12.24783039093018</v>
       </c>
       <c r="K11" t="n">
-        <v>11.56186294555664</v>
+        <v>11.22548365592957</v>
       </c>
       <c r="L11" t="n">
-        <v>13.68674757480621</v>
+        <v>12.27049462795258</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>12.63802099227905</v>
+        <v>15.14301323890686</v>
       </c>
       <c r="C12" t="n">
-        <v>15.00275683403015</v>
+        <v>12.08425140380859</v>
       </c>
       <c r="D12" t="n">
-        <v>14.05431461334229</v>
+        <v>12.55454421043396</v>
       </c>
       <c r="E12" t="n">
-        <v>16.02293753623962</v>
+        <v>13.81946587562561</v>
       </c>
       <c r="F12" t="n">
-        <v>14.05229902267456</v>
+        <v>12.61589384078979</v>
       </c>
       <c r="G12" t="n">
-        <v>14.5165810585022</v>
+        <v>12.40549254417419</v>
       </c>
       <c r="H12" t="n">
-        <v>11.85083818435669</v>
+        <v>13.24036073684692</v>
       </c>
       <c r="I12" t="n">
-        <v>13.93332695960999</v>
+        <v>12.51170086860657</v>
       </c>
       <c r="J12" t="n">
-        <v>13.66170692443848</v>
+        <v>15.13898801803589</v>
       </c>
       <c r="K12" t="n">
-        <v>11.61669039726257</v>
+        <v>14.15748357772827</v>
       </c>
       <c r="L12" t="n">
-        <v>13.73494725227356</v>
+        <v>13.36711943149567</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>12.57516002655029</v>
+        <v>13.63811469078064</v>
       </c>
       <c r="C13" t="n">
-        <v>13.19974207878113</v>
+        <v>13.84775137901306</v>
       </c>
       <c r="D13" t="n">
-        <v>14.90728092193604</v>
+        <v>12.30118107795715</v>
       </c>
       <c r="E13" t="n">
-        <v>13.18851327896118</v>
+        <v>13.84443664550781</v>
       </c>
       <c r="F13" t="n">
-        <v>15.4614896774292</v>
+        <v>13.05083179473877</v>
       </c>
       <c r="G13" t="n">
-        <v>13.98297429084778</v>
+        <v>12.05488109588623</v>
       </c>
       <c r="H13" t="n">
-        <v>13.42946839332581</v>
+        <v>14.64472675323486</v>
       </c>
       <c r="I13" t="n">
-        <v>15.53603625297546</v>
+        <v>13.14437413215637</v>
       </c>
       <c r="J13" t="n">
-        <v>13.82848119735718</v>
+        <v>16.15851140022278</v>
       </c>
       <c r="K13" t="n">
-        <v>12.35729932785034</v>
+        <v>13.21268916130066</v>
       </c>
       <c r="L13" t="n">
-        <v>13.84664454460144</v>
+        <v>13.58974981307983</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>11.83329510688782</v>
+        <v>12.39312076568604</v>
       </c>
       <c r="C14" t="n">
-        <v>13.8901801109314</v>
+        <v>12.14262104034424</v>
       </c>
       <c r="D14" t="n">
-        <v>12.37616491317749</v>
+        <v>12.94062161445618</v>
       </c>
       <c r="E14" t="n">
-        <v>12.37029790878296</v>
+        <v>12.80049467086792</v>
       </c>
       <c r="F14" t="n">
-        <v>17.44534754753113</v>
+        <v>13.62930154800415</v>
       </c>
       <c r="G14" t="n">
-        <v>11.78564119338989</v>
+        <v>12.23290586471558</v>
       </c>
       <c r="H14" t="n">
-        <v>12.37449193000793</v>
+        <v>11.90032696723938</v>
       </c>
       <c r="I14" t="n">
-        <v>17.24685907363892</v>
+        <v>12.50502872467041</v>
       </c>
       <c r="J14" t="n">
-        <v>11.57055163383484</v>
+        <v>12.4287109375</v>
       </c>
       <c r="K14" t="n">
-        <v>12.19543814659119</v>
+        <v>12.00787663459778</v>
       </c>
       <c r="L14" t="n">
-        <v>13.30882675647736</v>
+        <v>12.49810087680817</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>11.48571157455444</v>
+        <v>13.27400851249695</v>
       </c>
       <c r="C15" t="n">
-        <v>11.4997296333313</v>
+        <v>12.33944249153137</v>
       </c>
       <c r="D15" t="n">
-        <v>15.42489433288574</v>
+        <v>11.46279215812683</v>
       </c>
       <c r="E15" t="n">
-        <v>14.87235593795776</v>
+        <v>11.77451753616333</v>
       </c>
       <c r="F15" t="n">
-        <v>13.25662636756897</v>
+        <v>11.22095251083374</v>
       </c>
       <c r="G15" t="n">
-        <v>11.71048474311829</v>
+        <v>11.27086472511292</v>
       </c>
       <c r="H15" t="n">
-        <v>11.38743305206299</v>
+        <v>11.8219747543335</v>
       </c>
       <c r="I15" t="n">
-        <v>17.44682121276855</v>
+        <v>12.52170777320862</v>
       </c>
       <c r="J15" t="n">
-        <v>11.79340982437134</v>
+        <v>11.52124238014221</v>
       </c>
       <c r="K15" t="n">
-        <v>11.37350487709045</v>
+        <v>15.04069328308105</v>
       </c>
       <c r="L15" t="n">
-        <v>13.02509715557098</v>
+        <v>12.22481961250305</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>11.53995585441589</v>
+        <v>12.5056836605072</v>
       </c>
       <c r="C16" t="n">
-        <v>12.03007817268372</v>
+        <v>14.03428435325623</v>
       </c>
       <c r="D16" t="n">
-        <v>11.40029454231262</v>
+        <v>12.13167500495911</v>
       </c>
       <c r="E16" t="n">
-        <v>11.79608368873596</v>
+        <v>17.32043170928955</v>
       </c>
       <c r="F16" t="n">
-        <v>11.86397433280945</v>
+        <v>12.76698589324951</v>
       </c>
       <c r="G16" t="n">
-        <v>16.25093579292297</v>
+        <v>15.57385945320129</v>
       </c>
       <c r="H16" t="n">
-        <v>16.7312216758728</v>
+        <v>12.38458132743835</v>
       </c>
       <c r="I16" t="n">
-        <v>12.36008334159851</v>
+        <v>11.78305625915527</v>
       </c>
       <c r="J16" t="n">
-        <v>15.69566655158997</v>
+        <v>11.95406699180603</v>
       </c>
       <c r="K16" t="n">
-        <v>12.78900551795959</v>
+        <v>11.64933085441589</v>
       </c>
       <c r="L16" t="n">
-        <v>13.24572994709015</v>
+        <v>13.21039555072784</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>11.02018785476685</v>
+        <v>11.76308298110962</v>
       </c>
       <c r="C17" t="n">
-        <v>10.96018838882446</v>
+        <v>11.8528995513916</v>
       </c>
       <c r="D17" t="n">
-        <v>12.70583868026733</v>
+        <v>11.33963847160339</v>
       </c>
       <c r="E17" t="n">
-        <v>13.47497057914734</v>
+        <v>15.52813506126404</v>
       </c>
       <c r="F17" t="n">
-        <v>12.20799994468689</v>
+        <v>12.91763162612915</v>
       </c>
       <c r="G17" t="n">
-        <v>14.03468036651611</v>
+        <v>10.94865798950195</v>
       </c>
       <c r="H17" t="n">
-        <v>29.70310807228088</v>
+        <v>12.79375147819519</v>
       </c>
       <c r="I17" t="n">
-        <v>13.1928436756134</v>
+        <v>14.09141564369202</v>
       </c>
       <c r="J17" t="n">
-        <v>11.85503315925598</v>
+        <v>10.91213965415955</v>
       </c>
       <c r="K17" t="n">
-        <v>15.25434708595276</v>
+        <v>11.96137928962708</v>
       </c>
       <c r="L17" t="n">
-        <v>14.4409197807312</v>
+        <v>12.41087317466736</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>12.46002316474915</v>
+        <v>13.70135831832886</v>
       </c>
       <c r="C18" t="n">
-        <v>12.03232312202454</v>
+        <v>12.25319242477417</v>
       </c>
       <c r="D18" t="n">
-        <v>11.8572371006012</v>
+        <v>14.58537840843201</v>
       </c>
       <c r="E18" t="n">
-        <v>12.71772813796997</v>
+        <v>11.84887051582336</v>
       </c>
       <c r="F18" t="n">
-        <v>12.03440499305725</v>
+        <v>13.02497243881226</v>
       </c>
       <c r="G18" t="n">
-        <v>15.43589091300964</v>
+        <v>14.87965083122253</v>
       </c>
       <c r="H18" t="n">
-        <v>11.94270539283752</v>
+        <v>14.55112814903259</v>
       </c>
       <c r="I18" t="n">
-        <v>11.32762789726257</v>
+        <v>13.12413120269775</v>
       </c>
       <c r="J18" t="n">
-        <v>12.39132499694824</v>
+        <v>11.85282897949219</v>
       </c>
       <c r="K18" t="n">
-        <v>13.66863918304443</v>
+        <v>12.42842292785645</v>
       </c>
       <c r="L18" t="n">
-        <v>12.58679049015045</v>
+        <v>13.22499341964722</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>15.13420248031616</v>
+        <v>11.49329566955566</v>
       </c>
       <c r="C19" t="n">
-        <v>13.37410283088684</v>
+        <v>11.40199160575867</v>
       </c>
       <c r="D19" t="n">
-        <v>12.97883820533752</v>
+        <v>13.16100120544434</v>
       </c>
       <c r="E19" t="n">
-        <v>13.62265801429749</v>
+        <v>12.50665497779846</v>
       </c>
       <c r="F19" t="n">
-        <v>14.19180727005005</v>
+        <v>11.56608748435974</v>
       </c>
       <c r="G19" t="n">
-        <v>13.1631441116333</v>
+        <v>12.26631116867065</v>
       </c>
       <c r="H19" t="n">
-        <v>12.24892950057983</v>
+        <v>14.94410347938538</v>
       </c>
       <c r="I19" t="n">
-        <v>11.68641495704651</v>
+        <v>11.94112634658813</v>
       </c>
       <c r="J19" t="n">
-        <v>12.75997447967529</v>
+        <v>13.16996669769287</v>
       </c>
       <c r="K19" t="n">
-        <v>14.26456928253174</v>
+        <v>12.11270117759705</v>
       </c>
       <c r="L19" t="n">
-        <v>13.34246411323547</v>
+        <v>12.4563239812851</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>12.57529830932617</v>
+        <v>11.05188775062561</v>
       </c>
       <c r="C20" t="n">
-        <v>10.68955516815186</v>
+        <v>10.46139359474182</v>
       </c>
       <c r="D20" t="n">
-        <v>11.30004191398621</v>
+        <v>12.3400673866272</v>
       </c>
       <c r="E20" t="n">
-        <v>10.59532117843628</v>
+        <v>11.28379321098328</v>
       </c>
       <c r="F20" t="n">
-        <v>11.99865031242371</v>
+        <v>14.25065779685974</v>
       </c>
       <c r="G20" t="n">
-        <v>11.09591889381409</v>
+        <v>10.74039602279663</v>
       </c>
       <c r="H20" t="n">
-        <v>11.38724327087402</v>
+        <v>13.32359457015991</v>
       </c>
       <c r="I20" t="n">
-        <v>12.6508092880249</v>
+        <v>10.83644199371338</v>
       </c>
       <c r="J20" t="n">
-        <v>11.58991599082947</v>
+        <v>10.63294911384583</v>
       </c>
       <c r="K20" t="n">
-        <v>11.63634252548218</v>
+        <v>11.27335119247437</v>
       </c>
       <c r="L20" t="n">
-        <v>11.55190968513489</v>
+        <v>11.61945326328278</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>12.37511134147644</v>
+        <v>11.63044834136963</v>
       </c>
       <c r="C21" t="n">
-        <v>10.96323323249817</v>
+        <v>11.31965398788452</v>
       </c>
       <c r="D21" t="n">
-        <v>11.09402060508728</v>
+        <v>13.83096718788147</v>
       </c>
       <c r="E21" t="n">
-        <v>12.85738730430603</v>
+        <v>11.54212880134583</v>
       </c>
       <c r="F21" t="n">
-        <v>16.17639088630676</v>
+        <v>12.38104724884033</v>
       </c>
       <c r="G21" t="n">
-        <v>11.9670193195343</v>
+        <v>13.74852776527405</v>
       </c>
       <c r="H21" t="n">
-        <v>12.25795483589172</v>
+        <v>11.4474310874939</v>
       </c>
       <c r="I21" t="n">
-        <v>12.25571990013123</v>
+        <v>10.98154735565186</v>
       </c>
       <c r="J21" t="n">
-        <v>12.12340211868286</v>
+        <v>12.72912526130676</v>
       </c>
       <c r="K21" t="n">
-        <v>12.34222936630249</v>
+        <v>10.66236448287964</v>
       </c>
       <c r="L21" t="n">
-        <v>12.44124689102173</v>
+        <v>12.0273241519928</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>12.74474239349365</v>
+        <v>12.48424077033997</v>
       </c>
       <c r="C22" t="n">
-        <v>12.31624102592468</v>
+        <v>11.66816329956055</v>
       </c>
       <c r="D22" t="n">
-        <v>11.64690136909485</v>
+        <v>12.89448881149292</v>
       </c>
       <c r="E22" t="n">
-        <v>11.59446263313293</v>
+        <v>13.29277539253235</v>
       </c>
       <c r="F22" t="n">
-        <v>14.37647795677185</v>
+        <v>10.59706521034241</v>
       </c>
       <c r="G22" t="n">
-        <v>12.1827232837677</v>
+        <v>12.0869562625885</v>
       </c>
       <c r="H22" t="n">
-        <v>12.11549162864685</v>
+        <v>11.46940755844116</v>
       </c>
       <c r="I22" t="n">
-        <v>12.37405276298523</v>
+        <v>15.3761420249939</v>
       </c>
       <c r="J22" t="n">
-        <v>12.93141388893127</v>
+        <v>13.23938393592834</v>
       </c>
       <c r="K22" t="n">
-        <v>12.01815819740295</v>
+        <v>11.94608736038208</v>
       </c>
       <c r="L22" t="n">
-        <v>12.4300665140152</v>
+        <v>12.50547106266022</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>14.27740621566772</v>
+        <v>12.27375793457031</v>
       </c>
       <c r="C23" t="n">
-        <v>11.3074197769165</v>
+        <v>11.2524106502533</v>
       </c>
       <c r="D23" t="n">
-        <v>11.42793202400208</v>
+        <v>12.8697943687439</v>
       </c>
       <c r="E23" t="n">
-        <v>10.99761748313904</v>
+        <v>10.51973915100098</v>
       </c>
       <c r="F23" t="n">
-        <v>11.15666079521179</v>
+        <v>12.13069486618042</v>
       </c>
       <c r="G23" t="n">
-        <v>12.09747672080994</v>
+        <v>15.84670734405518</v>
       </c>
       <c r="H23" t="n">
-        <v>11.46816396713257</v>
+        <v>11.71876549720764</v>
       </c>
       <c r="I23" t="n">
-        <v>11.26001715660095</v>
+        <v>11.236811876297</v>
       </c>
       <c r="J23" t="n">
-        <v>10.98402738571167</v>
+        <v>14.36021089553833</v>
       </c>
       <c r="K23" t="n">
-        <v>11.26188182830811</v>
+        <v>11.35203909873962</v>
       </c>
       <c r="L23" t="n">
-        <v>11.62386033535004</v>
+        <v>12.35609316825867</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>12.45426106452942</v>
+        <v>12.07858395576477</v>
       </c>
       <c r="C24" t="n">
-        <v>14.35302424430847</v>
+        <v>11.41006231307983</v>
       </c>
       <c r="D24" t="n">
-        <v>11.96480584144592</v>
+        <v>11.48596739768982</v>
       </c>
       <c r="E24" t="n">
-        <v>15.40984559059143</v>
+        <v>14.05071997642517</v>
       </c>
       <c r="F24" t="n">
-        <v>11.83533382415771</v>
+        <v>12.49105668067932</v>
       </c>
       <c r="G24" t="n">
-        <v>12.25795936584473</v>
+        <v>12.51051712036133</v>
       </c>
       <c r="H24" t="n">
-        <v>12.90644788742065</v>
+        <v>11.07621669769287</v>
       </c>
       <c r="I24" t="n">
-        <v>12.59988808631897</v>
+        <v>12.86527156829834</v>
       </c>
       <c r="J24" t="n">
-        <v>11.07553291320801</v>
+        <v>13.46525120735168</v>
       </c>
       <c r="K24" t="n">
-        <v>12.75239014625549</v>
+        <v>11.67329978942871</v>
       </c>
       <c r="L24" t="n">
-        <v>12.76094889640808</v>
+        <v>12.31069467067718</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>13.62658643722534</v>
+        <v>13.22934055328369</v>
       </c>
       <c r="C25" t="n">
-        <v>15.68829607963562</v>
+        <v>14.02733063697815</v>
       </c>
       <c r="D25" t="n">
-        <v>14.18640351295471</v>
+        <v>14.57200503349304</v>
       </c>
       <c r="E25" t="n">
-        <v>12.92826986312866</v>
+        <v>12.60179018974304</v>
       </c>
       <c r="F25" t="n">
-        <v>13.66198921203613</v>
+        <v>13.80716419219971</v>
       </c>
       <c r="G25" t="n">
-        <v>13.11323642730713</v>
+        <v>12.9147572517395</v>
       </c>
       <c r="H25" t="n">
-        <v>15.24639987945557</v>
+        <v>16.18166780471802</v>
       </c>
       <c r="I25" t="n">
-        <v>13.3867769241333</v>
+        <v>15.91398358345032</v>
       </c>
       <c r="J25" t="n">
-        <v>12.43201041221619</v>
+        <v>13.71988582611084</v>
       </c>
       <c r="K25" t="n">
-        <v>13.87326836585999</v>
+        <v>13.1918158531189</v>
       </c>
       <c r="L25" t="n">
-        <v>13.81432371139526</v>
+        <v>14.01597409248352</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>9.877076864242554</v>
+        <v>9.884844779968262</v>
       </c>
       <c r="C26" t="n">
-        <v>11.38623285293579</v>
+        <v>11.13507080078125</v>
       </c>
       <c r="D26" t="n">
-        <v>9.937366485595703</v>
+        <v>10.27485823631287</v>
       </c>
       <c r="E26" t="n">
-        <v>12.67702722549438</v>
+        <v>9.91600513458252</v>
       </c>
       <c r="F26" t="n">
-        <v>14.61081600189209</v>
+        <v>11.19586968421936</v>
       </c>
       <c r="G26" t="n">
-        <v>10.33720970153809</v>
+        <v>10.11884641647339</v>
       </c>
       <c r="H26" t="n">
-        <v>13.62100434303284</v>
+        <v>10.39305329322815</v>
       </c>
       <c r="I26" t="n">
-        <v>11.4664614200592</v>
+        <v>10.28932237625122</v>
       </c>
       <c r="J26" t="n">
-        <v>11.00306630134583</v>
+        <v>11.10329055786133</v>
       </c>
       <c r="K26" t="n">
-        <v>10.78887891769409</v>
+        <v>9.9342200756073</v>
       </c>
       <c r="L26" t="n">
-        <v>11.57051401138306</v>
+        <v>10.42453813552856</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>12.21276783943176</v>
+        <v>14.75096035003662</v>
       </c>
       <c r="C27" t="n">
-        <v>12.23726320266724</v>
+        <v>12.28874349594116</v>
       </c>
       <c r="D27" t="n">
-        <v>13.93072152137756</v>
+        <v>12.1326060295105</v>
       </c>
       <c r="E27" t="n">
-        <v>12.89447379112244</v>
+        <v>16.88960194587708</v>
       </c>
       <c r="F27" t="n">
-        <v>12.51802039146423</v>
+        <v>11.76092863082886</v>
       </c>
       <c r="G27" t="n">
-        <v>12.05898690223694</v>
+        <v>11.27269983291626</v>
       </c>
       <c r="H27" t="n">
-        <v>14.02532935142517</v>
+        <v>12.03920841217041</v>
       </c>
       <c r="I27" t="n">
-        <v>15.30495548248291</v>
+        <v>11.9235417842865</v>
       </c>
       <c r="J27" t="n">
-        <v>14.68197989463806</v>
+        <v>12.57849097251892</v>
       </c>
       <c r="K27" t="n">
-        <v>14.09492468833923</v>
+        <v>15.98181366920471</v>
       </c>
       <c r="L27" t="n">
-        <v>13.39594230651855</v>
+        <v>13.1618595123291</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>11.97592878341675</v>
+        <v>11.84787726402283</v>
       </c>
       <c r="C28" t="n">
-        <v>10.60346245765686</v>
+        <v>12.57650375366211</v>
       </c>
       <c r="D28" t="n">
-        <v>11.61896777153015</v>
+        <v>11.5865318775177</v>
       </c>
       <c r="E28" t="n">
-        <v>11.47457218170166</v>
+        <v>11.57208204269409</v>
       </c>
       <c r="F28" t="n">
-        <v>12.55218815803528</v>
+        <v>11.88489270210266</v>
       </c>
       <c r="G28" t="n">
-        <v>12.38026475906372</v>
+        <v>11.50824427604675</v>
       </c>
       <c r="H28" t="n">
-        <v>11.64228534698486</v>
+        <v>10.97259068489075</v>
       </c>
       <c r="I28" t="n">
-        <v>11.09515023231506</v>
+        <v>11.62649583816528</v>
       </c>
       <c r="J28" t="n">
-        <v>10.62493801116943</v>
+        <v>11.17456388473511</v>
       </c>
       <c r="K28" t="n">
-        <v>11.77471113204956</v>
+        <v>11.99197840690613</v>
       </c>
       <c r="L28" t="n">
-        <v>11.57424688339233</v>
+        <v>11.67417607307434</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>10.18896722793579</v>
+        <v>11.59204196929932</v>
       </c>
       <c r="C29" t="n">
-        <v>11.6321542263031</v>
+        <v>11.19951176643372</v>
       </c>
       <c r="D29" t="n">
-        <v>10.30392956733704</v>
+        <v>10.23992991447449</v>
       </c>
       <c r="E29" t="n">
-        <v>10.08602285385132</v>
+        <v>11.84390354156494</v>
       </c>
       <c r="F29" t="n">
-        <v>10.94813466072083</v>
+        <v>10.70325088500977</v>
       </c>
       <c r="G29" t="n">
-        <v>10.2819709777832</v>
+        <v>11.58635473251343</v>
       </c>
       <c r="H29" t="n">
-        <v>11.73365783691406</v>
+        <v>10.11376976966858</v>
       </c>
       <c r="I29" t="n">
-        <v>10.75018978118896</v>
+        <v>12.62243509292603</v>
       </c>
       <c r="J29" t="n">
-        <v>15.83953046798706</v>
+        <v>11.06141376495361</v>
       </c>
       <c r="K29" t="n">
-        <v>10.31440734863281</v>
+        <v>10.27687191963196</v>
       </c>
       <c r="L29" t="n">
-        <v>11.20789649486542</v>
+        <v>11.12394833564758</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>15.65587186813354</v>
+        <v>14.4841091632843</v>
       </c>
       <c r="C30" t="n">
-        <v>15.6886100769043</v>
+        <v>12.11666965484619</v>
       </c>
       <c r="D30" t="n">
-        <v>13.71732473373413</v>
+        <v>11.67029571533203</v>
       </c>
       <c r="E30" t="n">
-        <v>11.49655723571777</v>
+        <v>11.1954984664917</v>
       </c>
       <c r="F30" t="n">
-        <v>14.05949807167053</v>
+        <v>13.77045941352844</v>
       </c>
       <c r="G30" t="n">
-        <v>12.16395878791809</v>
+        <v>15.57139682769775</v>
       </c>
       <c r="H30" t="n">
-        <v>11.13827800750732</v>
+        <v>11.01700830459595</v>
       </c>
       <c r="I30" t="n">
-        <v>11.64106011390686</v>
+        <v>13.44580006599426</v>
       </c>
       <c r="J30" t="n">
-        <v>14.53381657600403</v>
+        <v>11.54913139343262</v>
       </c>
       <c r="K30" t="n">
-        <v>12.04818844795227</v>
+        <v>15.48315691947937</v>
       </c>
       <c r="L30" t="n">
-        <v>13.21431639194489</v>
+        <v>13.03035259246826</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>13.56318116188049</v>
+        <v>19.03050470352173</v>
       </c>
       <c r="C31" t="n">
-        <v>12.87130188941956</v>
+        <v>11.47479557991028</v>
       </c>
       <c r="D31" t="n">
-        <v>11.57366371154785</v>
+        <v>11.27886557579041</v>
       </c>
       <c r="E31" t="n">
-        <v>17.90094327926636</v>
+        <v>16.84413814544678</v>
       </c>
       <c r="F31" t="n">
-        <v>12.15325379371643</v>
+        <v>12.65881872177124</v>
       </c>
       <c r="G31" t="n">
-        <v>13.0976574420929</v>
+        <v>15.50205540657043</v>
       </c>
       <c r="H31" t="n">
-        <v>15.79040122032166</v>
+        <v>12.62189531326294</v>
       </c>
       <c r="I31" t="n">
-        <v>13.52387523651123</v>
+        <v>11.86636281013489</v>
       </c>
       <c r="J31" t="n">
-        <v>11.89119029045105</v>
+        <v>11.50724029541016</v>
       </c>
       <c r="K31" t="n">
-        <v>12.64599227905273</v>
+        <v>11.49073481559753</v>
       </c>
       <c r="L31" t="n">
-        <v>13.50114603042602</v>
+        <v>13.42754113674164</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>16.42139554023743</v>
+        <v>12.56801104545593</v>
       </c>
       <c r="C32" t="n">
-        <v>11.51728320121765</v>
+        <v>12.46627974510193</v>
       </c>
       <c r="D32" t="n">
-        <v>12.01516771316528</v>
+        <v>12.08147549629211</v>
       </c>
       <c r="E32" t="n">
-        <v>12.66648411750793</v>
+        <v>11.1315712928772</v>
       </c>
       <c r="F32" t="n">
-        <v>11.77118515968323</v>
+        <v>11.61582374572754</v>
       </c>
       <c r="G32" t="n">
-        <v>12.76612377166748</v>
+        <v>11.10116291046143</v>
       </c>
       <c r="H32" t="n">
-        <v>11.71906757354736</v>
+        <v>16.21756625175476</v>
       </c>
       <c r="I32" t="n">
-        <v>11.97184658050537</v>
+        <v>12.76955938339233</v>
       </c>
       <c r="J32" t="n">
-        <v>11.2439661026001</v>
+        <v>15.22626900672913</v>
       </c>
       <c r="K32" t="n">
-        <v>11.32679724693298</v>
+        <v>11.55620384216309</v>
       </c>
       <c r="L32" t="n">
-        <v>12.34193170070648</v>
+        <v>12.67339227199554</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>13.22924399375916</v>
+        <v>14.67714166641235</v>
       </c>
       <c r="C33" t="n">
-        <v>12.9921727180481</v>
+        <v>13.56079626083374</v>
       </c>
       <c r="D33" t="n">
-        <v>15.69807076454163</v>
+        <v>11.86022686958313</v>
       </c>
       <c r="E33" t="n">
-        <v>11.52939176559448</v>
+        <v>16.29823470115662</v>
       </c>
       <c r="F33" t="n">
-        <v>14.21493530273438</v>
+        <v>12.22628211975098</v>
       </c>
       <c r="G33" t="n">
-        <v>11.80608010292053</v>
+        <v>15.01555109024048</v>
       </c>
       <c r="H33" t="n">
-        <v>12.40533709526062</v>
+        <v>11.63427972793579</v>
       </c>
       <c r="I33" t="n">
-        <v>13.96427965164185</v>
+        <v>12.00882077217102</v>
       </c>
       <c r="J33" t="n">
-        <v>12.36852383613586</v>
+        <v>11.70973896980286</v>
       </c>
       <c r="K33" t="n">
-        <v>15.36183547973633</v>
+        <v>12.53260588645935</v>
       </c>
       <c r="L33" t="n">
-        <v>13.35698707103729</v>
+        <v>13.15236780643463</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>11.01658487319946</v>
+        <v>11.89525437355042</v>
       </c>
       <c r="C34" t="n">
-        <v>10.95447492599487</v>
+        <v>10.53469848632812</v>
       </c>
       <c r="D34" t="n">
-        <v>10.94958972930908</v>
+        <v>10.6441011428833</v>
       </c>
       <c r="E34" t="n">
-        <v>10.62003779411316</v>
+        <v>10.9328031539917</v>
       </c>
       <c r="F34" t="n">
-        <v>14.04685306549072</v>
+        <v>12.83343648910522</v>
       </c>
       <c r="G34" t="n">
-        <v>13.05099725723267</v>
+        <v>11.64389491081238</v>
       </c>
       <c r="H34" t="n">
-        <v>13.78645038604736</v>
+        <v>10.26587891578674</v>
       </c>
       <c r="I34" t="n">
-        <v>11.78304648399353</v>
+        <v>11.34639048576355</v>
       </c>
       <c r="J34" t="n">
-        <v>11.61394453048706</v>
+        <v>12.7510461807251</v>
       </c>
       <c r="K34" t="n">
-        <v>11.38363170623779</v>
+        <v>13.90012097358704</v>
       </c>
       <c r="L34" t="n">
-        <v>11.92056107521057</v>
+        <v>11.67476251125336</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>13.3613715171814</v>
+        <v>13.48850560188293</v>
       </c>
       <c r="C35" t="n">
-        <v>11.89233231544495</v>
+        <v>14.20311546325684</v>
       </c>
       <c r="D35" t="n">
-        <v>11.09525418281555</v>
+        <v>11.70561742782593</v>
       </c>
       <c r="E35" t="n">
-        <v>11.32760405540466</v>
+        <v>11.79885339736938</v>
       </c>
       <c r="F35" t="n">
-        <v>11.90673279762268</v>
+        <v>16.53560614585876</v>
       </c>
       <c r="G35" t="n">
-        <v>12.6846878528595</v>
+        <v>11.79036116600037</v>
       </c>
       <c r="H35" t="n">
-        <v>14.75904726982117</v>
+        <v>11.86718559265137</v>
       </c>
       <c r="I35" t="n">
-        <v>11.28191471099854</v>
+        <v>11.65728163719177</v>
       </c>
       <c r="J35" t="n">
-        <v>13.13731646537781</v>
+        <v>11.53054451942444</v>
       </c>
       <c r="K35" t="n">
-        <v>11.48744130134583</v>
+        <v>11.9804539680481</v>
       </c>
       <c r="L35" t="n">
-        <v>12.29337024688721</v>
+        <v>12.65575249195099</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>11.37361645698547</v>
+        <v>11.6218101978302</v>
       </c>
       <c r="C36" t="n">
-        <v>11.88385152816772</v>
+        <v>11.22583723068237</v>
       </c>
       <c r="D36" t="n">
-        <v>12.71675729751587</v>
+        <v>12.36364936828613</v>
       </c>
       <c r="E36" t="n">
-        <v>11.73334383964539</v>
+        <v>11.54352927207947</v>
       </c>
       <c r="F36" t="n">
-        <v>14.42766976356506</v>
+        <v>16.26177358627319</v>
       </c>
       <c r="G36" t="n">
-        <v>10.97466206550598</v>
+        <v>12.65311932563782</v>
       </c>
       <c r="H36" t="n">
-        <v>14.13348197937012</v>
+        <v>11.5530104637146</v>
       </c>
       <c r="I36" t="n">
-        <v>12.47167658805847</v>
+        <v>12.62667798995972</v>
       </c>
       <c r="J36" t="n">
-        <v>11.32992744445801</v>
+        <v>11.66817498207092</v>
       </c>
       <c r="K36" t="n">
-        <v>11.43235349655151</v>
+        <v>11.5325756072998</v>
       </c>
       <c r="L36" t="n">
-        <v>12.24773404598236</v>
+        <v>12.30501580238342</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>11.87636542320251</v>
+        <v>11.22505593299866</v>
       </c>
       <c r="C37" t="n">
-        <v>12.62004923820496</v>
+        <v>12.93062400817871</v>
       </c>
       <c r="D37" t="n">
-        <v>10.96977376937866</v>
+        <v>11.68379807472229</v>
       </c>
       <c r="E37" t="n">
-        <v>11.39200925827026</v>
+        <v>11.63142323493958</v>
       </c>
       <c r="F37" t="n">
-        <v>11.15427303314209</v>
+        <v>11.6573657989502</v>
       </c>
       <c r="G37" t="n">
-        <v>13.10787153244019</v>
+        <v>11.86280107498169</v>
       </c>
       <c r="H37" t="n">
-        <v>14.04736638069153</v>
+        <v>11.31769371032715</v>
       </c>
       <c r="I37" t="n">
-        <v>11.03389024734497</v>
+        <v>13.00189924240112</v>
       </c>
       <c r="J37" t="n">
-        <v>11.02471041679382</v>
+        <v>11.49926161766052</v>
       </c>
       <c r="K37" t="n">
-        <v>11.26618647575378</v>
+        <v>11.37655663490295</v>
       </c>
       <c r="L37" t="n">
-        <v>11.84924957752228</v>
+        <v>11.81864793300629</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>11.0919976234436</v>
+        <v>12.61677861213684</v>
       </c>
       <c r="C38" t="n">
-        <v>11.34098052978516</v>
+        <v>12.57833313941956</v>
       </c>
       <c r="D38" t="n">
-        <v>12.31748700141907</v>
+        <v>16.67066764831543</v>
       </c>
       <c r="E38" t="n">
-        <v>11.60331702232361</v>
+        <v>11.2702693939209</v>
       </c>
       <c r="F38" t="n">
-        <v>10.96611857414246</v>
+        <v>12.31302213668823</v>
       </c>
       <c r="G38" t="n">
-        <v>11.61272788047791</v>
+        <v>11.26128435134888</v>
       </c>
       <c r="H38" t="n">
-        <v>12.98132061958313</v>
+        <v>11.64180636405945</v>
       </c>
       <c r="I38" t="n">
-        <v>10.83800172805786</v>
+        <v>11.27069163322449</v>
       </c>
       <c r="J38" t="n">
-        <v>11.15832996368408</v>
+        <v>29.04510998725891</v>
       </c>
       <c r="K38" t="n">
-        <v>13.14252638816833</v>
+        <v>17.96230459213257</v>
       </c>
       <c r="L38" t="n">
-        <v>11.70528073310852</v>
+        <v>14.66302678585052</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>10.72982478141785</v>
+        <v>11.08776664733887</v>
       </c>
       <c r="C39" t="n">
-        <v>10.80480790138245</v>
+        <v>13.51757526397705</v>
       </c>
       <c r="D39" t="n">
-        <v>10.60564088821411</v>
+        <v>10.16919350624084</v>
       </c>
       <c r="E39" t="n">
-        <v>10.73874306678772</v>
+        <v>10.16464018821716</v>
       </c>
       <c r="F39" t="n">
-        <v>12.91102004051208</v>
+        <v>10.24249505996704</v>
       </c>
       <c r="G39" t="n">
-        <v>10.09045433998108</v>
+        <v>11.13716650009155</v>
       </c>
       <c r="H39" t="n">
-        <v>10.37895965576172</v>
+        <v>10.23606157302856</v>
       </c>
       <c r="I39" t="n">
-        <v>10.68768739700317</v>
+        <v>10.40163493156433</v>
       </c>
       <c r="J39" t="n">
-        <v>11.74047327041626</v>
+        <v>13.68918752670288</v>
       </c>
       <c r="K39" t="n">
-        <v>11.4382221698761</v>
+        <v>12.71118068695068</v>
       </c>
       <c r="L39" t="n">
-        <v>11.01258335113525</v>
+        <v>11.3356901884079</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>13.59619879722595</v>
+        <v>13.07476401329041</v>
       </c>
       <c r="C40" t="n">
-        <v>11.98418235778809</v>
+        <v>11.93749189376831</v>
       </c>
       <c r="D40" t="n">
-        <v>12.83764457702637</v>
+        <v>14.75815868377686</v>
       </c>
       <c r="E40" t="n">
-        <v>12.52135968208313</v>
+        <v>14.25498652458191</v>
       </c>
       <c r="F40" t="n">
-        <v>11.99849987030029</v>
+        <v>12.07611536979675</v>
       </c>
       <c r="G40" t="n">
-        <v>12.16453790664673</v>
+        <v>12.82666611671448</v>
       </c>
       <c r="H40" t="n">
-        <v>11.36710333824158</v>
+        <v>13.18124008178711</v>
       </c>
       <c r="I40" t="n">
-        <v>15.41448545455933</v>
+        <v>12.73948693275452</v>
       </c>
       <c r="J40" t="n">
-        <v>11.6917941570282</v>
+        <v>11.60339951515198</v>
       </c>
       <c r="K40" t="n">
-        <v>11.47117757797241</v>
+        <v>12.16589617729187</v>
       </c>
       <c r="L40" t="n">
-        <v>12.50469837188721</v>
+        <v>12.86182053089142</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>12.70803713798523</v>
+        <v>14.45849108695984</v>
       </c>
       <c r="C41" t="n">
-        <v>10.49533534049988</v>
+        <v>15.27034592628479</v>
       </c>
       <c r="D41" t="n">
-        <v>12.20098733901978</v>
+        <v>9.899775505065918</v>
       </c>
       <c r="E41" t="n">
-        <v>12.82418990135193</v>
+        <v>10.63137578964233</v>
       </c>
       <c r="F41" t="n">
-        <v>10.3694064617157</v>
+        <v>13.46600389480591</v>
       </c>
       <c r="G41" t="n">
-        <v>10.20360159873962</v>
+        <v>13.04761981964111</v>
       </c>
       <c r="H41" t="n">
-        <v>13.45448422431946</v>
+        <v>10.58897280693054</v>
       </c>
       <c r="I41" t="n">
-        <v>10.3584566116333</v>
+        <v>14.1533145904541</v>
       </c>
       <c r="J41" t="n">
-        <v>10.67453670501709</v>
+        <v>12.19774866104126</v>
       </c>
       <c r="K41" t="n">
-        <v>10.570148229599</v>
+        <v>14.39955425262451</v>
       </c>
       <c r="L41" t="n">
-        <v>11.3859183549881</v>
+        <v>12.81132023334503</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>12.643714427948</v>
+        <v>11.55645108222961</v>
       </c>
       <c r="C42" t="n">
-        <v>10.89039754867554</v>
+        <v>18.46169710159302</v>
       </c>
       <c r="D42" t="n">
-        <v>11.57648897171021</v>
+        <v>11.92315721511841</v>
       </c>
       <c r="E42" t="n">
-        <v>11.88488745689392</v>
+        <v>17.03269100189209</v>
       </c>
       <c r="F42" t="n">
-        <v>13.64458560943604</v>
+        <v>12.32251572608948</v>
       </c>
       <c r="G42" t="n">
-        <v>14.26640796661377</v>
+        <v>17.00585126876831</v>
       </c>
       <c r="H42" t="n">
-        <v>11.79325199127197</v>
+        <v>15.18265628814697</v>
       </c>
       <c r="I42" t="n">
-        <v>11.47492718696594</v>
+        <v>14.09385824203491</v>
       </c>
       <c r="J42" t="n">
-        <v>12.69530558586121</v>
+        <v>12.42173194885254</v>
       </c>
       <c r="K42" t="n">
-        <v>12.41556406021118</v>
+        <v>12.70562314987183</v>
       </c>
       <c r="L42" t="n">
-        <v>12.32855308055878</v>
+        <v>14.27062330245972</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>11.7187442779541</v>
+        <v>14.34722995758057</v>
       </c>
       <c r="C43" t="n">
-        <v>13.06279611587524</v>
+        <v>12.63752388954163</v>
       </c>
       <c r="D43" t="n">
-        <v>12.96764183044434</v>
+        <v>12.83443188667297</v>
       </c>
       <c r="E43" t="n">
-        <v>12.41552233695984</v>
+        <v>12.42640447616577</v>
       </c>
       <c r="F43" t="n">
-        <v>11.98798489570618</v>
+        <v>12.52864980697632</v>
       </c>
       <c r="G43" t="n">
-        <v>12.67411088943481</v>
+        <v>12.67727851867676</v>
       </c>
       <c r="H43" t="n">
-        <v>14.24764466285706</v>
+        <v>11.15410590171814</v>
       </c>
       <c r="I43" t="n">
-        <v>12.59653782844543</v>
+        <v>12.44137763977051</v>
       </c>
       <c r="J43" t="n">
-        <v>11.22366714477539</v>
+        <v>13.59143829345703</v>
       </c>
       <c r="K43" t="n">
-        <v>11.60550498962402</v>
+        <v>14.40684032440186</v>
       </c>
       <c r="L43" t="n">
-        <v>12.45001549720764</v>
+        <v>12.90452806949616</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>12.98770499229431</v>
+        <v>11.92317986488342</v>
       </c>
       <c r="C44" t="n">
-        <v>12.64593935012817</v>
+        <v>16.52765679359436</v>
       </c>
       <c r="D44" t="n">
-        <v>12.04034090042114</v>
+        <v>13.30438852310181</v>
       </c>
       <c r="E44" t="n">
-        <v>15.37111949920654</v>
+        <v>16.48261713981628</v>
       </c>
       <c r="F44" t="n">
-        <v>12.85451769828796</v>
+        <v>12.86059999465942</v>
       </c>
       <c r="G44" t="n">
-        <v>14.96974635124207</v>
+        <v>12.96380162239075</v>
       </c>
       <c r="H44" t="n">
-        <v>15.43372750282288</v>
+        <v>15.20550441741943</v>
       </c>
       <c r="I44" t="n">
-        <v>12.06572651863098</v>
+        <v>12.74140763282776</v>
       </c>
       <c r="J44" t="n">
-        <v>12.15209078788757</v>
+        <v>12.49212574958801</v>
       </c>
       <c r="K44" t="n">
-        <v>12.78393363952637</v>
+        <v>12.72446012496948</v>
       </c>
       <c r="L44" t="n">
-        <v>13.3304847240448</v>
+        <v>13.72257418632507</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>13.84302520751953</v>
+        <v>10.74946713447571</v>
       </c>
       <c r="C45" t="n">
-        <v>13.88499689102173</v>
+        <v>10.57511806488037</v>
       </c>
       <c r="D45" t="n">
-        <v>13.23736190795898</v>
+        <v>10.95064616203308</v>
       </c>
       <c r="E45" t="n">
-        <v>10.98918771743774</v>
+        <v>12.30520343780518</v>
       </c>
       <c r="F45" t="n">
-        <v>13.48026776313782</v>
+        <v>10.02649736404419</v>
       </c>
       <c r="G45" t="n">
-        <v>10.79164028167725</v>
+        <v>11.2085165977478</v>
       </c>
       <c r="H45" t="n">
-        <v>11.29824495315552</v>
+        <v>11.59601283073425</v>
       </c>
       <c r="I45" t="n">
-        <v>11.97828984260559</v>
+        <v>10.7836000919342</v>
       </c>
       <c r="J45" t="n">
-        <v>9.700611114501953</v>
+        <v>10.30129265785217</v>
       </c>
       <c r="K45" t="n">
-        <v>11.42856097221375</v>
+        <v>10.76613187789917</v>
       </c>
       <c r="L45" t="n">
-        <v>12.06321866512299</v>
+        <v>10.92624862194061</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>12.56140303611755</v>
+        <v>12.64586710929871</v>
       </c>
       <c r="C46" t="n">
-        <v>12.20524311065674</v>
+        <v>14.67583298683167</v>
       </c>
       <c r="D46" t="n">
-        <v>12.81448245048523</v>
+        <v>13.74193620681763</v>
       </c>
       <c r="E46" t="n">
-        <v>13.41552686691284</v>
+        <v>12.6229944229126</v>
       </c>
       <c r="F46" t="n">
-        <v>15.36679983139038</v>
+        <v>12.30818128585815</v>
       </c>
       <c r="G46" t="n">
-        <v>12.74366211891174</v>
+        <v>12.93359923362732</v>
       </c>
       <c r="H46" t="n">
-        <v>12.66837382316589</v>
+        <v>12.31629085540771</v>
       </c>
       <c r="I46" t="n">
-        <v>13.92630457878113</v>
+        <v>12.3860285282135</v>
       </c>
       <c r="J46" t="n">
-        <v>14.78586506843567</v>
+        <v>15.42833161354065</v>
       </c>
       <c r="K46" t="n">
-        <v>12.20632338523865</v>
+        <v>14.06569671630859</v>
       </c>
       <c r="L46" t="n">
-        <v>13.26939842700958</v>
+        <v>13.31247589588165</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>11.93186354637146</v>
+        <v>13.11613345146179</v>
       </c>
       <c r="C47" t="n">
-        <v>12.634850025177</v>
+        <v>11.20098924636841</v>
       </c>
       <c r="D47" t="n">
-        <v>11.67156505584717</v>
+        <v>12.43638968467712</v>
       </c>
       <c r="E47" t="n">
-        <v>14.50829076766968</v>
+        <v>11.81892943382263</v>
       </c>
       <c r="F47" t="n">
-        <v>12.27808618545532</v>
+        <v>10.86584448814392</v>
       </c>
       <c r="G47" t="n">
-        <v>14.89912986755371</v>
+        <v>11.39649391174316</v>
       </c>
       <c r="H47" t="n">
-        <v>12.19958472251892</v>
+        <v>11.43138146400452</v>
       </c>
       <c r="I47" t="n">
-        <v>11.47582674026489</v>
+        <v>11.46682548522949</v>
       </c>
       <c r="J47" t="n">
-        <v>13.29005408287048</v>
+        <v>13.01096487045288</v>
       </c>
       <c r="K47" t="n">
-        <v>12.53433752059937</v>
+        <v>13.31261348724365</v>
       </c>
       <c r="L47" t="n">
-        <v>12.7423588514328</v>
+        <v>12.00565655231476</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>11.85019493103027</v>
+        <v>12.03139328956604</v>
       </c>
       <c r="C48" t="n">
-        <v>12.96812534332275</v>
+        <v>12.38947486877441</v>
       </c>
       <c r="D48" t="n">
-        <v>12.77450799942017</v>
+        <v>13.01886582374573</v>
       </c>
       <c r="E48" t="n">
-        <v>12.50794529914856</v>
+        <v>13.18179655075073</v>
       </c>
       <c r="F48" t="n">
-        <v>12.53567600250244</v>
+        <v>12.7601330280304</v>
       </c>
       <c r="G48" t="n">
-        <v>13.32956147193909</v>
+        <v>13.30487084388733</v>
       </c>
       <c r="H48" t="n">
-        <v>15.06116580963135</v>
+        <v>12.23283219337463</v>
       </c>
       <c r="I48" t="n">
-        <v>14.04567337036133</v>
+        <v>11.76555848121643</v>
       </c>
       <c r="J48" t="n">
-        <v>13.91228365898132</v>
+        <v>11.50026273727417</v>
       </c>
       <c r="K48" t="n">
-        <v>14.51807236671448</v>
+        <v>14.77140378952026</v>
       </c>
       <c r="L48" t="n">
-        <v>13.35032062530518</v>
+        <v>12.69565916061401</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>11.89973425865173</v>
+        <v>11.85111212730408</v>
       </c>
       <c r="C49" t="n">
-        <v>12.68682813644409</v>
+        <v>12.4516658782959</v>
       </c>
       <c r="D49" t="n">
-        <v>12.09625673294067</v>
+        <v>11.39544939994812</v>
       </c>
       <c r="E49" t="n">
-        <v>16.53983807563782</v>
+        <v>11.52503061294556</v>
       </c>
       <c r="F49" t="n">
-        <v>13.15080761909485</v>
+        <v>12.0524480342865</v>
       </c>
       <c r="G49" t="n">
-        <v>14.32213950157166</v>
+        <v>11.18353986740112</v>
       </c>
       <c r="H49" t="n">
-        <v>13.76601672172546</v>
+        <v>14.76793479919434</v>
       </c>
       <c r="I49" t="n">
-        <v>12.63903522491455</v>
+        <v>11.72871065139771</v>
       </c>
       <c r="J49" t="n">
-        <v>12.6800377368927</v>
+        <v>11.60648965835571</v>
       </c>
       <c r="K49" t="n">
-        <v>12.86890387535095</v>
+        <v>11.93315529823303</v>
       </c>
       <c r="L49" t="n">
-        <v>13.26495978832245</v>
+        <v>12.04955363273621</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>12.23771953582764</v>
+        <v>11.4458966255188</v>
       </c>
       <c r="C50" t="n">
-        <v>14.73559284210205</v>
+        <v>12.02441000938416</v>
       </c>
       <c r="D50" t="n">
-        <v>12.35376858711243</v>
+        <v>11.33863854408264</v>
       </c>
       <c r="E50" t="n">
-        <v>15.58199763298035</v>
+        <v>12.14311957359314</v>
       </c>
       <c r="F50" t="n">
-        <v>15.39375782012939</v>
+        <v>12.96152830123901</v>
       </c>
       <c r="G50" t="n">
-        <v>11.87994122505188</v>
+        <v>11.41497135162354</v>
       </c>
       <c r="H50" t="n">
-        <v>13.04739761352539</v>
+        <v>14.05024600028992</v>
       </c>
       <c r="I50" t="n">
-        <v>12.03421831130981</v>
+        <v>14.46168828010559</v>
       </c>
       <c r="J50" t="n">
-        <v>12.42429089546204</v>
+        <v>11.25823974609375</v>
       </c>
       <c r="K50" t="n">
-        <v>12.28384494781494</v>
+        <v>11.77730059623718</v>
       </c>
       <c r="L50" t="n">
-        <v>13.19725294113159</v>
+        <v>12.28760390281677</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>12.96886563301086</v>
+        <v>12.28525495529175</v>
       </c>
       <c r="C51" t="n">
-        <v>12.03193044662476</v>
+        <v>10.94334506988525</v>
       </c>
       <c r="D51" t="n">
-        <v>12.16090726852417</v>
+        <v>11.14284658432007</v>
       </c>
       <c r="E51" t="n">
-        <v>12.26737999916077</v>
+        <v>11.49789309501648</v>
       </c>
       <c r="F51" t="n">
-        <v>12.48631167411804</v>
+        <v>12.25383353233337</v>
       </c>
       <c r="G51" t="n">
-        <v>12.80824375152588</v>
+        <v>12.17801880836487</v>
       </c>
       <c r="H51" t="n">
-        <v>11.99657893180847</v>
+        <v>11.11823105812073</v>
       </c>
       <c r="I51" t="n">
-        <v>12.6211302280426</v>
+        <v>11.3188419342041</v>
       </c>
       <c r="J51" t="n">
-        <v>11.64310050010681</v>
+        <v>11.21099400520325</v>
       </c>
       <c r="K51" t="n">
-        <v>11.50264382362366</v>
+        <v>12.02244877815247</v>
       </c>
       <c r="L51" t="n">
-        <v>12.2487092256546</v>
+        <v>11.59717078208923</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>12.50946002006531</v>
+        <v>12.58262991905212</v>
       </c>
       <c r="C52" t="n">
-        <v>12.39937707424164</v>
+        <v>12.59513319015503</v>
       </c>
       <c r="D52" t="n">
-        <v>12.22558531284332</v>
+        <v>12.10569682598114</v>
       </c>
       <c r="E52" t="n">
-        <v>12.75502747535706</v>
+        <v>12.72588992118835</v>
       </c>
       <c r="F52" t="n">
-        <v>13.09819278240204</v>
+        <v>12.36172054290772</v>
       </c>
       <c r="G52" t="n">
-        <v>12.54806489944458</v>
+        <v>12.53942940235138</v>
       </c>
       <c r="H52" t="n">
-        <v>13.15376465797424</v>
+        <v>12.29209221363068</v>
       </c>
       <c r="I52" t="n">
-        <v>12.4233594417572</v>
+        <v>12.18906075954437</v>
       </c>
       <c r="J52" t="n">
-        <v>12.27820030212402</v>
+        <v>12.61620295524597</v>
       </c>
       <c r="K52" t="n">
-        <v>12.19370456218719</v>
+        <v>12.59694539546967</v>
       </c>
       <c r="L52" t="n">
-        <v>12.55847365283966</v>
+        <v>12.46048011255264</v>
       </c>
     </row>
   </sheetData>
